--- a/output/pdf_financials_xlsx/MKO.xlsx
+++ b/output/pdf_financials_xlsx/MKO.xlsx
@@ -499,10 +499,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C5" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C5" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D5" s="1" t="inlineStr">
         <is>
@@ -521,10 +519,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C6" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C6" s="3" t="n">
+        <v>7.931102</v>
       </c>
       <c r="D6" s="1" t="inlineStr">
         <is>
@@ -543,10 +539,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C7" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C7" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D7" s="1" t="inlineStr">
         <is>
@@ -565,10 +559,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C8" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C8" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D8" s="1" t="inlineStr">
         <is>
@@ -587,10 +579,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C9" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C9" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D9" s="1" t="inlineStr">
         <is>
@@ -609,10 +599,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C10" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C10" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D10" s="1" t="inlineStr">
         <is>
@@ -631,10 +619,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C11" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C11" s="3" t="n">
+        <v>7.931102</v>
       </c>
       <c r="D11" s="1" t="inlineStr">
         <is>
@@ -653,10 +639,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C12" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C12" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D12" s="1" t="inlineStr">
         <is>
@@ -675,10 +659,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C13" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C13" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D13" s="1" t="inlineStr">
         <is>
@@ -697,10 +679,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C14" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C14" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D14" s="1" t="inlineStr">
         <is>
@@ -719,10 +699,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C15" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C15" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D15" s="1" t="inlineStr">
         <is>
@@ -741,10 +719,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C16" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C16" s="3" t="n">
+        <v>-1.053939</v>
       </c>
       <c r="D16" s="1" t="inlineStr">
         <is>
@@ -763,10 +739,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C17" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C17" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D17" s="1" t="inlineStr">
         <is>
@@ -829,10 +803,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C20" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C20" s="3" t="n">
+        <v>-1.053939</v>
       </c>
       <c r="D20" s="1" t="inlineStr">
         <is>
@@ -851,10 +823,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C21" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C21" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D21" s="1" t="inlineStr">
         <is>
@@ -873,10 +843,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C22" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C22" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D22" s="1" t="inlineStr">
         <is>
@@ -895,10 +863,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C23" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C23" s="3" t="n">
+        <v>-1.053939</v>
       </c>
       <c r="D23" s="1" t="inlineStr">
         <is>
@@ -983,10 +949,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C27" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C27" s="3" t="n">
+        <v>-1.053939</v>
       </c>
       <c r="D27" s="1" t="inlineStr">
         <is>
@@ -1025,10 +989,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C29" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C29" s="3" t="n">
+        <v>-1.095878</v>
       </c>
       <c r="D29" s="1" t="inlineStr">
         <is>
@@ -1047,10 +1009,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C30" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C30" s="3" t="n">
+        <v>-13.81747454515148</v>
       </c>
       <c r="D30" s="1" t="inlineStr">
         <is>
@@ -1069,10 +1029,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C31" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C31" s="3" t="n">
+        <v>-0</v>
       </c>
       <c r="D31" s="1" t="inlineStr">
         <is>
@@ -1091,10 +1049,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C32" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C32" s="3" t="n">
+        <v>-13.28868295982072</v>
       </c>
       <c r="D32" s="1" t="inlineStr">
         <is>
@@ -1131,20 +1087,14 @@
           <t xml:space="preserve">    Marketable Securities</t>
         </is>
       </c>
-      <c r="B35" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C35" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D35" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B35" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C35" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D35" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="36">
@@ -1153,20 +1103,14 @@
           <t xml:space="preserve">  Cash, Cash Equivalents, Marketable Securities</t>
         </is>
       </c>
-      <c r="B36" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C36" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D36" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B36" s="3" t="n">
+        <v>0.835268</v>
+      </c>
+      <c r="C36" s="3" t="n">
+        <v>3.361</v>
+      </c>
+      <c r="D36" s="3" t="n">
+        <v>4.253</v>
       </c>
     </row>
     <row r="37">
@@ -1175,20 +1119,14 @@
           <t xml:space="preserve">    Accounts Receivable</t>
         </is>
       </c>
-      <c r="B37" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C37" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D37" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B37" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C37" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D37" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="38">
@@ -1197,20 +1135,14 @@
           <t xml:space="preserve">    Notes Receivable</t>
         </is>
       </c>
-      <c r="B38" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C38" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D38" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B38" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C38" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D38" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="39">
@@ -1219,20 +1151,14 @@
           <t xml:space="preserve">    Loans Receivable</t>
         </is>
       </c>
-      <c r="B39" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C39" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D39" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B39" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C39" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D39" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="40">
@@ -1241,20 +1167,14 @@
           <t xml:space="preserve">    Other Current Receivables</t>
         </is>
       </c>
-      <c r="B40" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C40" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D40" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B40" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C40" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D40" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="41">
@@ -1263,20 +1183,14 @@
           <t xml:space="preserve">  Total Receivables</t>
         </is>
       </c>
-      <c r="B41" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C41" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D41" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B41" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C41" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D41" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="42">
@@ -1285,20 +1199,14 @@
           <t xml:space="preserve">    Inventories, Raw Materials &amp; Components</t>
         </is>
       </c>
-      <c r="B42" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C42" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D42" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B42" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C42" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D42" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="43">
@@ -1307,20 +1215,14 @@
           <t xml:space="preserve">    Inventories, Work In Process</t>
         </is>
       </c>
-      <c r="B43" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C43" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D43" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B43" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C43" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D43" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="44">
@@ -1329,20 +1231,14 @@
           <t xml:space="preserve">    Inventories, Inventories Adjustments</t>
         </is>
       </c>
-      <c r="B44" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C44" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D44" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B44" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C44" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D44" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="45">
@@ -1351,20 +1247,14 @@
           <t xml:space="preserve">    Inventories, Finished Goods</t>
         </is>
       </c>
-      <c r="B45" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C45" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D45" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B45" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C45" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D45" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="46">
@@ -1373,20 +1263,14 @@
           <t xml:space="preserve">    Inventories, Other</t>
         </is>
       </c>
-      <c r="B46" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C46" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D46" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B46" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C46" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D46" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="47">
@@ -1395,10 +1279,8 @@
           <t xml:space="preserve">  Total Inventories</t>
         </is>
       </c>
-      <c r="B47" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B47" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C47" s="3" t="n">
         <v>11.017</v>
@@ -1413,20 +1295,14 @@
           <t xml:space="preserve">  Other Current Assets</t>
         </is>
       </c>
-      <c r="B48" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C48" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D48" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B48" s="3" t="n">
+        <v>0.027712</v>
+      </c>
+      <c r="C48" s="3" t="n">
+        <v>3.079</v>
+      </c>
+      <c r="D48" s="3" t="n">
+        <v>1.684</v>
       </c>
     </row>
     <row r="49">
@@ -1451,20 +1327,14 @@
           <t xml:space="preserve">  Investments And Advances</t>
         </is>
       </c>
-      <c r="B50" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C50" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D50" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B50" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C50" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D50" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="51">
@@ -1473,20 +1343,14 @@
           <t xml:space="preserve">      Land And Improvements</t>
         </is>
       </c>
-      <c r="B51" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C51" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D51" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B51" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C51" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D51" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="52">
@@ -1495,20 +1359,14 @@
           <t xml:space="preserve">      Buildings And Improvements</t>
         </is>
       </c>
-      <c r="B52" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C52" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D52" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B52" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C52" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D52" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="53">
@@ -1517,20 +1375,14 @@
           <t xml:space="preserve">      Machinery, Furniture, Equipment</t>
         </is>
       </c>
-      <c r="B53" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C53" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D53" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B53" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C53" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D53" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="54">
@@ -1539,20 +1391,14 @@
           <t xml:space="preserve">      Construction In Progress</t>
         </is>
       </c>
-      <c r="B54" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C54" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D54" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B54" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C54" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D54" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="55">
@@ -1583,20 +1429,14 @@
           <t xml:space="preserve">    Gross Property, Plant and Equipment</t>
         </is>
       </c>
-      <c r="B56" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C56" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D56" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B56" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C56" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D56" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="57">
@@ -1605,20 +1445,14 @@
           <t xml:space="preserve">    Accumulated Depreciation</t>
         </is>
       </c>
-      <c r="B57" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C57" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D57" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B57" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C57" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D57" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="58">
@@ -1628,13 +1462,13 @@
         </is>
       </c>
       <c r="B58" s="3" t="n">
-        <v>0.059756</v>
+        <v>4.560682</v>
       </c>
       <c r="C58" s="3" t="n">
-        <v>0.063</v>
+        <v>0.093</v>
       </c>
       <c r="D58" s="3" t="n">
-        <v>0.005</v>
+        <v>0.006</v>
       </c>
     </row>
     <row r="59">
@@ -1643,20 +1477,14 @@
           <t xml:space="preserve">  Intangible Assets</t>
         </is>
       </c>
-      <c r="B59" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C59" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D59" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B59" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C59" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D59" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="60">
@@ -1665,20 +1493,14 @@
           <t xml:space="preserve">    Goodwill</t>
         </is>
       </c>
-      <c r="B60" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C60" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D60" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B60" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C60" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D60" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="61">
@@ -1687,20 +1509,14 @@
           <t xml:space="preserve">  Other Long Term Assets</t>
         </is>
       </c>
-      <c r="B61" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C61" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D61" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B61" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C61" s="3" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="D61" s="3" t="n">
+        <v>10.764</v>
       </c>
     </row>
     <row r="62">
@@ -1709,20 +1525,14 @@
           <t xml:space="preserve">  Total Long-Term Assets</t>
         </is>
       </c>
-      <c r="B62" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C62" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D62" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B62" s="3" t="n">
+        <v>4.560682</v>
+      </c>
+      <c r="C62" s="3" t="n">
+        <v>0.6929999999999999</v>
+      </c>
+      <c r="D62" s="3" t="n">
+        <v>10.77</v>
       </c>
     </row>
     <row r="63">
@@ -1747,20 +1557,14 @@
           <t xml:space="preserve">    Accounts Payable</t>
         </is>
       </c>
-      <c r="B64" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C64" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D64" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B64" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C64" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D64" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="65">
@@ -1769,20 +1573,14 @@
           <t xml:space="preserve">    Total Tax Payable</t>
         </is>
       </c>
-      <c r="B65" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C65" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D65" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B65" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C65" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D65" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="66">
@@ -1791,20 +1589,14 @@
           <t xml:space="preserve">    Other Current Payables</t>
         </is>
       </c>
-      <c r="B66" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C66" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D66" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B66" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C66" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D66" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="67">
@@ -1813,20 +1605,14 @@
           <t xml:space="preserve">    Current Accrued Expense</t>
         </is>
       </c>
-      <c r="B67" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C67" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D67" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B67" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C67" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D67" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="68">
@@ -1851,20 +1637,14 @@
           <t xml:space="preserve">    Short-Term Debt</t>
         </is>
       </c>
-      <c r="B69" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C69" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D69" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B69" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C69" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D69" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="70">
@@ -1873,20 +1653,14 @@
           <t xml:space="preserve">    Short-Term Capital Lease Obligation</t>
         </is>
       </c>
-      <c r="B70" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C70" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D70" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B70" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C70" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D70" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="71">
@@ -1895,20 +1669,14 @@
           <t xml:space="preserve">  Short-Term Debt &amp; Capital Lease Obligation</t>
         </is>
       </c>
-      <c r="B71" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C71" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D71" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B71" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C71" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D71" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="72">
@@ -1917,20 +1685,14 @@
           <t xml:space="preserve">    Current Deferred Revenue</t>
         </is>
       </c>
-      <c r="B72" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C72" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D72" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B72" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C72" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D72" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="73">
@@ -1939,20 +1701,14 @@
           <t xml:space="preserve">    Current Deferred Taxes Liabilities</t>
         </is>
       </c>
-      <c r="B73" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C73" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D73" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B73" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C73" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D73" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="74">
@@ -1961,20 +1717,14 @@
           <t xml:space="preserve">  Deferred Tax And Revenue</t>
         </is>
       </c>
-      <c r="B74" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C74" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D74" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B74" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C74" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D74" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="75">
@@ -1983,20 +1733,14 @@
           <t xml:space="preserve">  Other Current Liabilities</t>
         </is>
       </c>
-      <c r="B75" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C75" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D75" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B75" s="3" t="n">
+        <v>1.125775</v>
+      </c>
+      <c r="C75" s="3" t="n">
+        <v>3.139</v>
+      </c>
+      <c r="D75" s="3" t="n">
+        <v>7.493</v>
       </c>
     </row>
     <row r="76">
@@ -2021,20 +1765,14 @@
           <t xml:space="preserve">    Long-Term Debt</t>
         </is>
       </c>
-      <c r="B77" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C77" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D77" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B77" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C77" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D77" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="78">
@@ -2043,20 +1781,14 @@
           <t xml:space="preserve">    Long-Term Capital Lease Obligation</t>
         </is>
       </c>
-      <c r="B78" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C78" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D78" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B78" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C78" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D78" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="79">
@@ -2065,20 +1797,14 @@
           <t xml:space="preserve">  Long-Term Debt &amp; Capital Lease Obligation</t>
         </is>
       </c>
-      <c r="B79" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C79" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D79" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B79" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C79" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D79" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="80">
@@ -2109,20 +1835,14 @@
           <t xml:space="preserve">  Pension And Retirement Benefit</t>
         </is>
       </c>
-      <c r="B81" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C81" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D81" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B81" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C81" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D81" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="82">
@@ -2131,20 +1851,14 @@
           <t xml:space="preserve">    NonCurrent Deferred Revenue</t>
         </is>
       </c>
-      <c r="B82" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C82" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D82" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B82" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C82" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D82" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="83">
@@ -2153,20 +1867,14 @@
           <t xml:space="preserve">  NonCurrent Deferred Liabilities</t>
         </is>
       </c>
-      <c r="B83" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C83" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D83" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B83" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C83" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D83" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="84">
@@ -2175,20 +1883,14 @@
           <t xml:space="preserve">  NonCurrent Deferred Income Tax</t>
         </is>
       </c>
-      <c r="B84" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C84" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D84" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B84" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C84" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D84" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="85">
@@ -2197,20 +1899,14 @@
           <t xml:space="preserve">  Other Long-Term Liabilities</t>
         </is>
       </c>
-      <c r="B85" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C85" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D85" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B85" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C85" s="3" t="n">
+        <v>2.091</v>
+      </c>
+      <c r="D85" s="3" t="n">
+        <v>1.592</v>
       </c>
     </row>
     <row r="86">
@@ -2219,20 +1915,14 @@
           <t xml:space="preserve">  Total Long-Term Liabilities</t>
         </is>
       </c>
-      <c r="B86" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C86" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D86" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B86" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C86" s="3" t="n">
+        <v>2.091</v>
+      </c>
+      <c r="D86" s="3" t="n">
+        <v>1.592</v>
       </c>
     </row>
     <row r="87">
@@ -2257,20 +1947,14 @@
           <t xml:space="preserve">  Common Stock</t>
         </is>
       </c>
-      <c r="B88" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C88" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D88" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B88" s="3" t="n">
+        <v>36.055299</v>
+      </c>
+      <c r="C88" s="3" t="n">
+        <v>50.078</v>
+      </c>
+      <c r="D88" s="3" t="n">
+        <v>70.295</v>
       </c>
     </row>
     <row r="89">
@@ -2279,20 +1963,14 @@
           <t xml:space="preserve">  Preferred Stock</t>
         </is>
       </c>
-      <c r="B89" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C89" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D89" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B89" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C89" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D89" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="90">
@@ -2323,20 +2001,14 @@
           <t xml:space="preserve">  Accumulated other comprehensive income (loss)</t>
         </is>
       </c>
-      <c r="B91" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C91" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D91" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B91" s="3" t="n">
+        <v>0.420913</v>
+      </c>
+      <c r="C91" s="3" t="n">
+        <v>-0.633</v>
+      </c>
+      <c r="D91" s="3" t="n">
+        <v>1.577</v>
       </c>
     </row>
     <row r="92">
@@ -2361,20 +2033,14 @@
           <t xml:space="preserve">  Treasury Stock</t>
         </is>
       </c>
-      <c r="B93" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C93" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D93" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B93" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C93" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D93" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="94">
@@ -2383,20 +2049,14 @@
           <t xml:space="preserve">  Total Stockholders Equity</t>
         </is>
       </c>
-      <c r="B94" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C94" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D94" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B94" s="3" t="n">
+        <v>4.049068</v>
+      </c>
+      <c r="C94" s="3" t="n">
+        <v>-7.823</v>
+      </c>
+      <c r="D94" s="3" t="n">
+        <v>6.054</v>
       </c>
     </row>
     <row r="95">
@@ -2405,20 +2065,14 @@
           <t xml:space="preserve">  Minority Interest</t>
         </is>
       </c>
-      <c r="B95" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C95" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D95" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B95" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C95" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D95" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="96">
@@ -2427,20 +2081,14 @@
           <t>Total Equity</t>
         </is>
       </c>
-      <c r="B96" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C96" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D96" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B96" s="3" t="n">
+        <v>4.049068</v>
+      </c>
+      <c r="C96" s="3" t="n">
+        <v>-7.823</v>
+      </c>
+      <c r="D96" s="3" t="n">
+        <v>6.054</v>
       </c>
     </row>
     <row r="97">
@@ -2449,20 +2097,14 @@
           <t>Equity-to-Asset</t>
         </is>
       </c>
-      <c r="B97" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C97" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D97" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B97" s="3" t="n">
+        <v>0.7465561091380695</v>
+      </c>
+      <c r="C97" s="3" t="n">
+        <v>-0.4310192837465565</v>
+      </c>
+      <c r="D97" s="3" t="n">
+        <v>0.3392927198341086</v>
       </c>
     </row>
     <row r="98">
@@ -2483,10 +2125,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C99" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C99" s="3" t="n">
+        <v>-1.053939</v>
       </c>
       <c r="D99" s="1" t="inlineStr">
         <is>
@@ -2523,15 +2163,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C101" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D101" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C101" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D101" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="102">
@@ -2545,15 +2181,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C102" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D102" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C102" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D102" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="103">
@@ -2567,15 +2199,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C103" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D103" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C103" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D103" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="104">
@@ -2589,15 +2217,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C104" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D104" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C104" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D104" s="3" t="n">
+        <v>4.754</v>
       </c>
     </row>
     <row r="105">
@@ -2611,15 +2235,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C105" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D105" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C105" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D105" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="106">
@@ -2633,15 +2253,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C106" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D106" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C106" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D106" s="3" t="n">
+        <v>4.754</v>
       </c>
     </row>
     <row r="107">
@@ -2655,15 +2271,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C107" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D107" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C107" s="3" t="n">
+        <v>0.395</v>
+      </c>
+      <c r="D107" s="3" t="n">
+        <v>0.657</v>
       </c>
     </row>
     <row r="108">
@@ -2677,15 +2289,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C108" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D108" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C108" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D108" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="109">
@@ -2699,15 +2307,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C109" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D109" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C109" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D109" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="110">
@@ -2721,15 +2325,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C110" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D110" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C110" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D110" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="111">
@@ -2743,15 +2343,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C111" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D111" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C111" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D111" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="112">
@@ -2765,15 +2361,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C112" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D112" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C112" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D112" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="113">
@@ -2787,15 +2379,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C113" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D113" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C113" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D113" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="114">
@@ -2809,15 +2397,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C114" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D114" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C114" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D114" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="115">
@@ -2831,15 +2415,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C115" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D115" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C115" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D115" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="116">
@@ -2853,15 +2433,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C116" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D116" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C116" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D116" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="117">
@@ -2875,15 +2451,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C117" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D117" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C117" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D117" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="118">
@@ -2897,15 +2469,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C118" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D118" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C118" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D118" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="119">
@@ -2941,15 +2509,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C120" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D120" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C120" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D120" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="121">
@@ -2963,15 +2527,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C121" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D121" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C121" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D121" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="122">
@@ -2985,15 +2545,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C122" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D122" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C122" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D122" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="123">
@@ -3007,15 +2563,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C123" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D123" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C123" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D123" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="124">
@@ -3029,15 +2581,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C124" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D124" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C124" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D124" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="125">
@@ -3051,15 +2599,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C125" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D125" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C125" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D125" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="126">
@@ -3073,15 +2617,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C126" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D126" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C126" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D126" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="127">
@@ -3117,15 +2657,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C128" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D128" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C128" s="3" t="n">
+        <v>3.371936</v>
+      </c>
+      <c r="D128" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="129">
@@ -3160,10 +2696,8 @@
       <c r="C130" s="3" t="n">
         <v>0.835268</v>
       </c>
-      <c r="D130" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D130" s="3" t="n">
+        <v>3.361</v>
       </c>
     </row>
     <row r="131">
@@ -3177,15 +2711,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C131" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D131" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C131" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D131" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="132">
@@ -3200,12 +2730,10 @@
         </is>
       </c>
       <c r="C132" s="3" t="n">
-        <v>2.52578</v>
-      </c>
-      <c r="D132" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>2.526</v>
+      </c>
+      <c r="D132" s="3" t="n">
+        <v>0.892</v>
       </c>
     </row>
     <row r="133">
@@ -3237,15 +2765,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C134" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D134" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C134" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D134" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="135">
@@ -3504,7 +3028,11 @@
           <t>Exploration and evaluation assets 7 765 7 65</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr"/>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NetPPE</t>
+        </is>
+      </c>
       <c r="E7" t="inlineStr">
         <is>
           <t>-</t>
@@ -3921,7 +3449,11 @@
           <t>Accumulated other comprehensive income (loss) 3,634</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr"/>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>GainsLossesNotAffectingRetainedEarnings</t>
+        </is>
+      </c>
       <c r="E20" t="inlineStr">
         <is>
           <t>-</t>
@@ -3950,7 +3482,11 @@
           <t>Total shareholders' equity (deficit) 1 6,910</t>
         </is>
       </c>
-      <c r="D21" t="inlineStr"/>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>StockholdersEquity</t>
+        </is>
+      </c>
       <c r="E21" t="inlineStr">
         <is>
           <t>-</t>
@@ -4229,7 +3765,11 @@
           <t>Exploration and evaluation assets 9 765,000</t>
         </is>
       </c>
-      <c r="D30" t="inlineStr"/>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>NetPPE</t>
+        </is>
+      </c>
       <c r="E30" s="5" t="n">
         <v>4.500926</v>
       </c>
@@ -4619,7 +4159,11 @@
           <t>Accumulated other comprehensive income (loss) 1,577,440</t>
         </is>
       </c>
-      <c r="D42" t="inlineStr"/>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>GainsLossesNotAffectingRetainedEarnings</t>
+        </is>
+      </c>
       <c r="E42" s="5" t="n">
         <v>0.420913</v>
       </c>
@@ -4648,7 +4192,11 @@
           <t>Total shareholders' equity (deficit) 6,054,291</t>
         </is>
       </c>
-      <c r="D43" t="inlineStr"/>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>StockholdersEquity</t>
+        </is>
+      </c>
       <c r="E43" s="5" t="n">
         <v>4.049068</v>
       </c>
@@ -4985,7 +4533,11 @@
           <t>Gain on settlement of accounts payable - (</t>
         </is>
       </c>
-      <c r="D54" t="inlineStr"/>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>ChangeInPayablesAndAccruedExpense</t>
+        </is>
+      </c>
       <c r="E54" t="inlineStr">
         <is>
           <t>-</t>
@@ -5045,7 +4597,11 @@
           <t>Share-based payments 6 24</t>
         </is>
       </c>
-      <c r="D56" t="inlineStr"/>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>StockBasedCompensation</t>
+        </is>
+      </c>
       <c r="E56" t="inlineStr">
         <is>
           <t>-</t>
@@ -5380,7 +4936,11 @@
           <t>Change in cash and cash equivalents (1,620)</t>
         </is>
       </c>
-      <c r="D67" t="inlineStr"/>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>ChangesInCash</t>
+        </is>
+      </c>
       <c r="E67" t="inlineStr">
         <is>
           <t>-</t>
@@ -5731,7 +5291,11 @@
           <t>Share-based payments 657,041</t>
         </is>
       </c>
-      <c r="D78" t="inlineStr"/>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>StockBasedCompensation</t>
+        </is>
+      </c>
       <c r="E78" t="inlineStr">
         <is>
           <t>-</t>
@@ -5823,7 +5387,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>(4,856,935) (</t>
+          <t>Non-cash items total</t>
         </is>
       </c>
       <c r="D81" t="inlineStr"/>
@@ -6078,7 +5642,11 @@
           <t>Proceeds on issue of shares, net of share issuance costs 20,184,235</t>
         </is>
       </c>
-      <c r="D89" t="inlineStr"/>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>NetOtherFinancingCharges</t>
+        </is>
+      </c>
       <c r="E89" t="inlineStr">
         <is>
           <t>-</t>
@@ -6534,11 +6102,7 @@
           <t>Interest income 7 3 5 18</t>
         </is>
       </c>
-      <c r="D103" t="inlineStr">
-        <is>
-          <t>InterestIncome</t>
-        </is>
-      </c>
+      <c r="D103" t="inlineStr"/>
       <c r="E103" t="inlineStr">
         <is>
           <t>-</t>
@@ -7345,7 +6909,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>(14,656,926)</t>
+          <t>Cost of sales total</t>
         </is>
       </c>
       <c r="D129" t="inlineStr"/>
@@ -7885,7 +7449,11 @@
           <t>Other comprehensive income (loss) for the period 2,210,466</t>
         </is>
       </c>
-      <c r="D146" t="inlineStr"/>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
       <c r="E146" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/MKO.xlsx
+++ b/output/pdf_financials_xlsx/MKO.xlsx
@@ -431,6 +431,12 @@
   </sheetPr>
   <dimension ref="A1:D135"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="56" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">

--- a/output/pdf_financials_xlsx/MKO.xlsx
+++ b/output/pdf_financials_xlsx/MKO.xlsx
@@ -486,12 +486,10 @@
         </is>
       </c>
       <c r="C4" s="3" t="n">
-        <v>7.931102</v>
-      </c>
-      <c r="D4" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>7.931</v>
+      </c>
+      <c r="D4" s="3" t="n">
+        <v>8.583</v>
       </c>
     </row>
     <row r="5">
@@ -508,10 +506,8 @@
       <c r="C5" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D5" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D5" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -526,12 +522,10 @@
         </is>
       </c>
       <c r="C6" s="3" t="n">
-        <v>7.931102</v>
-      </c>
-      <c r="D6" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>7.931</v>
+      </c>
+      <c r="D6" s="3" t="n">
+        <v>8.583</v>
       </c>
     </row>
     <row r="7">
@@ -548,10 +542,8 @@
       <c r="C7" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D7" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D7" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -568,10 +560,8 @@
       <c r="C8" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D8" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D8" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -588,10 +578,8 @@
       <c r="C9" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D9" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D9" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -608,10 +596,8 @@
       <c r="C10" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D10" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D10" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -626,12 +612,10 @@
         </is>
       </c>
       <c r="C11" s="3" t="n">
-        <v>7.931102</v>
-      </c>
-      <c r="D11" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>7.931</v>
+      </c>
+      <c r="D11" s="3" t="n">
+        <v>8.583</v>
       </c>
     </row>
     <row r="12">
@@ -648,10 +632,8 @@
       <c r="C12" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D12" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D12" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -666,12 +648,10 @@
         </is>
       </c>
       <c r="C13" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D13" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0</v>
+      </c>
+      <c r="D13" s="3" t="n">
+        <v>-0</v>
       </c>
     </row>
     <row r="14">
@@ -688,10 +668,8 @@
       <c r="C14" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D14" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D14" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -708,10 +686,8 @@
       <c r="C15" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D15" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D15" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -726,12 +702,10 @@
         </is>
       </c>
       <c r="C16" s="3" t="n">
-        <v>-1.053939</v>
-      </c>
-      <c r="D16" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-25.304</v>
+      </c>
+      <c r="D16" s="3" t="n">
+        <v>-25.297</v>
       </c>
     </row>
     <row r="17">
@@ -746,12 +720,10 @@
         </is>
       </c>
       <c r="C17" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D17" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.075</v>
+      </c>
+      <c r="D17" s="3" t="n">
+        <v>0.068</v>
       </c>
     </row>
     <row r="18">
@@ -810,12 +782,10 @@
         </is>
       </c>
       <c r="C20" s="3" t="n">
-        <v>-1.053939</v>
-      </c>
-      <c r="D20" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-25.229</v>
+      </c>
+      <c r="D20" s="3" t="n">
+        <v>-25.229</v>
       </c>
     </row>
     <row r="21">
@@ -832,10 +802,8 @@
       <c r="C21" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D21" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D21" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="22">
@@ -852,10 +820,8 @@
       <c r="C22" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D22" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D22" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="23">
@@ -870,12 +836,10 @@
         </is>
       </c>
       <c r="C23" s="3" t="n">
-        <v>-1.053939</v>
-      </c>
-      <c r="D23" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-25.229</v>
+      </c>
+      <c r="D23" s="3" t="n">
+        <v>-25.229</v>
       </c>
     </row>
     <row r="24">
@@ -956,12 +920,10 @@
         </is>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-1.053939</v>
-      </c>
-      <c r="D27" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-25.304</v>
+      </c>
+      <c r="D27" s="3" t="n">
+        <v>-25.297</v>
       </c>
     </row>
     <row r="28">
@@ -976,12 +938,10 @@
         </is>
       </c>
       <c r="C28" s="3" t="n">
-        <v>-0.041939</v>
-      </c>
-      <c r="D28" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.042</v>
+      </c>
+      <c r="D28" s="3" t="n">
+        <v>0.061</v>
       </c>
     </row>
     <row r="29">
@@ -996,12 +956,10 @@
         </is>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-1.095878</v>
-      </c>
-      <c r="D29" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-25.262</v>
+      </c>
+      <c r="D29" s="3" t="n">
+        <v>-25.236</v>
       </c>
     </row>
     <row r="30">
@@ -1016,12 +974,10 @@
         </is>
       </c>
       <c r="C30" s="3" t="n">
-        <v>-13.81747454515148</v>
-      </c>
-      <c r="D30" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-318.5222544445845</v>
+      </c>
+      <c r="D30" s="3" t="n">
+        <v>-294.023068857043</v>
       </c>
     </row>
     <row r="31">
@@ -1036,12 +992,10 @@
         </is>
       </c>
       <c r="C31" s="3" t="n">
-        <v>-0</v>
-      </c>
-      <c r="D31" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.2963958267467594</v>
+      </c>
+      <c r="D31" s="3" t="n">
+        <v>-0.2688065778550816</v>
       </c>
     </row>
     <row r="32">
@@ -1056,12 +1010,10 @@
         </is>
       </c>
       <c r="C32" s="3" t="n">
-        <v>-13.28868295982072</v>
-      </c>
-      <c r="D32" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-318.1061656789812</v>
+      </c>
+      <c r="D32" s="3" t="n">
+        <v>-293.9415122917395</v>
       </c>
     </row>
     <row r="33">
@@ -1471,10 +1423,10 @@
         <v>4.560682</v>
       </c>
       <c r="C58" s="3" t="n">
-        <v>0.093</v>
+        <v>0.6929999999999999</v>
       </c>
       <c r="D58" s="3" t="n">
-        <v>0.006</v>
+        <v>10.77</v>
       </c>
     </row>
     <row r="59">
@@ -1519,10 +1471,10 @@
         <v>0</v>
       </c>
       <c r="C61" s="3" t="n">
-        <v>0.6</v>
+        <v>0</v>
       </c>
       <c r="D61" s="3" t="n">
-        <v>10.764</v>
+        <v>0</v>
       </c>
     </row>
     <row r="62">
@@ -2132,12 +2084,10 @@
         </is>
       </c>
       <c r="C99" s="3" t="n">
-        <v>-1.053939</v>
-      </c>
-      <c r="D99" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-25.229</v>
+      </c>
+      <c r="D99" s="3" t="n">
+        <v>-25.229</v>
       </c>
     </row>
     <row r="100">
@@ -2152,10 +2102,10 @@
         </is>
       </c>
       <c r="C100" s="3" t="n">
-        <v>0.005</v>
+        <v>0.065</v>
       </c>
       <c r="D100" s="3" t="n">
-        <v>0.006</v>
+        <v>0.07099999999999999</v>
       </c>
     </row>
     <row r="101">
@@ -2227,7 +2177,7 @@
         <v>0</v>
       </c>
       <c r="D104" s="3" t="n">
-        <v>4.754</v>
+        <v>-4.754</v>
       </c>
     </row>
     <row r="105">
@@ -2260,10 +2210,10 @@
         </is>
       </c>
       <c r="C106" s="3" t="n">
-        <v>0</v>
+        <v>-1.948</v>
       </c>
       <c r="D106" s="3" t="n">
-        <v>4.754</v>
+        <v>-4.555</v>
       </c>
     </row>
     <row r="107">
@@ -2493,15 +2443,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C119" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D119" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C119" s="3" t="n">
+        <v>3.125</v>
+      </c>
+      <c r="D119" s="3" t="n">
+        <v>-9.9</v>
       </c>
     </row>
     <row r="120">
@@ -2685,7 +2631,7 @@
         <v>6.375</v>
       </c>
       <c r="D129" s="3" t="n">
-        <v>0.205</v>
+        <v>20.205</v>
       </c>
     </row>
     <row r="130">
@@ -2700,7 +2646,7 @@
         </is>
       </c>
       <c r="C130" s="3" t="n">
-        <v>0.835268</v>
+        <v>0.835</v>
       </c>
       <c r="D130" s="3" t="n">
         <v>3.361</v>
@@ -2789,15 +2735,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C135" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D135" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C135" s="3" t="n">
+        <v>-6.974</v>
+      </c>
+      <c r="D135" s="3" t="n">
+        <v>-9.413</v>
       </c>
     </row>
   </sheetData>
@@ -2811,7 +2753,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G171"/>
+  <dimension ref="A1:G211"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -2965,7 +2907,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Prepaid expenses, and other 209 2 79</t>
+          <t>Prepaid expenses, and other 209</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -2979,10 +2921,10 @@
         </is>
       </c>
       <c r="F5" s="5" t="n">
-        <v>0.054</v>
+        <v>0.154</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>0.001</v>
+        <v>0.279</v>
       </c>
     </row>
     <row r="6">
@@ -3031,7 +2973,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Exploration and evaluation assets 7 765 7 65</t>
+          <t>Exploration and evaluation assets 7 765</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -3045,10 +2987,10 @@
         </is>
       </c>
       <c r="F7" s="5" t="n">
-        <v>0.03</v>
+        <v>0.13</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>0.001</v>
+        <v>0.765</v>
       </c>
     </row>
     <row r="8">
@@ -3064,7 +3006,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Mineral property, plant and equipment 8 4 5,298 10,005</t>
+          <t>Mineral property, plant and equipment 8 45,298</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -3078,10 +3020,10 @@
         </is>
       </c>
       <c r="F8" s="5" t="n">
-        <v>0.063</v>
+        <v>0.5629999999999999</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>0.005</v>
+        <v>10.005</v>
       </c>
     </row>
     <row r="9">
@@ -3097,7 +3039,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>TOTAL ASSETS $ 4 9,429 $</t>
+          <t>TOTAL ASSETS $ 49,429 $</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -3223,7 +3165,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Total current liabilities 1 6,535</t>
+          <t>Total current liabilities 16,535</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -3256,7 +3198,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Accounts payable and accrued liabilities 9 - 8</t>
+          <t>Accounts payable and accrued liabilities 9 -</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -3275,7 +3217,7 @@
         </is>
       </c>
       <c r="G14" s="5" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.87</v>
       </c>
     </row>
     <row r="15">
@@ -3291,7 +3233,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Provision for reclamation and rehabilitation 10 834 7</t>
+          <t>Provision for reclamation and rehabilitation 10 834</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -3304,7 +3246,7 @@
         <v>2.091</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>0.022</v>
+        <v>0.722</v>
       </c>
     </row>
     <row r="16">
@@ -3320,7 +3262,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Term loan 11 1 5,150</t>
+          <t>Term loan 11 15,150</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
@@ -3353,7 +3295,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Total liabilities 3 2,519</t>
+          <t>Total liabilities 32,519</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3386,7 +3328,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Share capital 12 8 7,262</t>
+          <t>Share capital 12 87,262</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3419,7 +3361,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Contributed surplus 1 1,634</t>
+          <t>Contributed surplus 11,634</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -3480,29 +3422,25 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Deficit (85,620) ( 73,491) ( 64,216)</t>
+          <t>Shareholders' equity (deficit)</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Total shareholders' equity (deficit) 1 6,910</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>StockholdersEquity</t>
-        </is>
-      </c>
+          <t>Deficit (85,620)</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
       <c r="F21" s="5" t="n">
-        <v>-7.823</v>
+        <v>-64.21599999999999</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>6.054</v>
+        <v>-73.491</v>
       </c>
     </row>
     <row r="22">
@@ -3513,17 +3451,17 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Deficit (85,620) ( 73,491) ( 64,216)</t>
+          <t>Shareholders' equity (deficit)</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>TOTAL LIABILITIES AND SHAREHOLDERS' EQUITY $ 4 9,429 $</t>
+          <t>Total shareholders' equity (deficit) 16,910</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>TotalLiabilitiesAndTotalEquityGrossMinorityInterest</t>
+          <t>StockholdersEquity</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -3532,10 +3470,10 @@
         </is>
       </c>
       <c r="F22" s="5" t="n">
-        <v>18.15</v>
+        <v>-7.823</v>
       </c>
       <c r="G22" s="5" t="n">
-        <v>17.843</v>
+        <v>6.054</v>
       </c>
     </row>
     <row r="23">
@@ -3546,25 +3484,29 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Deficit (85,620) ( 73,491) ( 64,216)</t>
+          <t>Shareholders' equity (deficit)</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Approved by the Audit Committee of the Board of Directors on April</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
+          <t>TOTAL LIABILITIES AND SHAREHOLDERS' EQUITY $ 49,429 $</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>TotalLiabilitiesAndTotalEquityGrossMinorityInterest</t>
+        </is>
+      </c>
       <c r="E23" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
       <c r="F23" s="5" t="n">
-        <v>2.021</v>
+        <v>18.15</v>
       </c>
       <c r="G23" s="5" t="n">
-        <v>0.028</v>
+        <v>17.843</v>
       </c>
     </row>
     <row r="24">
@@ -3573,23 +3515,27 @@
           <t>balance_sheet</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr"/>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Shareholders' equity (deficit)</t>
+        </is>
+      </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Note December 31, 2019 April 30, 2019 May</t>
+          <t>Approved by the Audit Committee of the Board of Directors on April</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
-      <c r="E24" s="5" t="n">
-        <v>0.002018</v>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F24" s="5" t="n">
-        <v>1e-06</v>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>2.021</v>
+      </c>
+      <c r="G24" s="5" t="n">
+        <v>0.028</v>
       </c>
     </row>
     <row r="25">
@@ -3598,26 +3544,18 @@
           <t>balance_sheet</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>Current</t>
-        </is>
-      </c>
+      <c r="B25" t="inlineStr"/>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Cash and cash equivalents 4,253,102</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>CashAndCashEquivalents</t>
-        </is>
-      </c>
+          <t>Note December 31, 2019 April 30, 2019 May</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr"/>
       <c r="E25" s="5" t="n">
-        <v>0.835268</v>
+        <v>0.002018</v>
       </c>
       <c r="F25" s="5" t="n">
-        <v>3.361048</v>
+        <v>1e-06</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
@@ -3638,15 +3576,19 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Receivables and refundable taxes 7 1,404,568</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
+          <t>Cash and cash equivalents 4,253,102</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>CashAndCashEquivalents</t>
+        </is>
+      </c>
       <c r="E26" s="5" t="n">
-        <v>0.011962</v>
+        <v>0.835268</v>
       </c>
       <c r="F26" s="5" t="n">
-        <v>2.924579</v>
+        <v>3.361048</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
@@ -3667,21 +3609,15 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Inventories 8 1,136,299</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>Inventory</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Receivables and refundable taxes 7 1,404,568</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr"/>
+      <c r="E27" s="5" t="n">
+        <v>0.011962</v>
       </c>
       <c r="F27" s="5" t="n">
-        <v>11.017043</v>
+        <v>2.924579</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
@@ -3702,19 +3638,21 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Prepaid expenses, and other 279,044</t>
+          <t>Inventories 8 1,136,299</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>PrepaidAssets</t>
-        </is>
-      </c>
-      <c r="E28" s="5" t="n">
-        <v>0.01575</v>
+          <t>Inventory</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F28" s="5" t="n">
-        <v>0.153372</v>
+        <v>11.017043</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
@@ -3735,19 +3673,19 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Total current assets 7,073,013</t>
+          <t>Prepaid expenses, and other 279,044</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>CurrentAssets</t>
+          <t>PrepaidAssets</t>
         </is>
       </c>
       <c r="E29" s="5" t="n">
-        <v>0.86298</v>
+        <v>0.01575</v>
       </c>
       <c r="F29" s="5" t="n">
-        <v>17.456042</v>
+        <v>0.153372</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
@@ -3768,19 +3706,19 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Exploration and evaluation assets 9 765,000</t>
+          <t>Total current assets 7,073,013</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NetPPE</t>
+          <t>CurrentAssets</t>
         </is>
       </c>
       <c r="E30" s="5" t="n">
-        <v>4.500926</v>
+        <v>0.86298</v>
       </c>
       <c r="F30" s="5" t="n">
-        <v>0.129635</v>
+        <v>17.456042</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
@@ -3801,7 +3739,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Mineral property, plant and equipment 10 10,005,324</t>
+          <t>Exploration and evaluation assets 9 765,000</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -3810,10 +3748,10 @@
         </is>
       </c>
       <c r="E31" s="5" t="n">
-        <v>0.059756</v>
+        <v>4.500926</v>
       </c>
       <c r="F31" s="5" t="n">
-        <v>0.563414</v>
+        <v>0.129635</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
@@ -3834,19 +3772,19 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>TOTAL ASSETS 17,843,337</t>
+          <t>Mineral property, plant and equipment 10 10,005,324</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>TotalAssets</t>
+          <t>NetPPE</t>
         </is>
       </c>
       <c r="E32" s="5" t="n">
-        <v>5.423662</v>
+        <v>0.059756</v>
       </c>
       <c r="F32" s="5" t="n">
-        <v>18.149091</v>
+        <v>0.563414</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
@@ -3862,24 +3800,24 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Current liabilities</t>
+          <t>Current</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Accounts payable and accrued liabilities 11 8,783,714</t>
+          <t>TOTAL ASSETS 17,843,337</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>PayablesAndAccruedExpenses</t>
+          <t>TotalAssets</t>
         </is>
       </c>
       <c r="E33" s="5" t="n">
-        <v>0.248819</v>
+        <v>5.423662</v>
       </c>
       <c r="F33" s="5" t="n">
-        <v>20.743438</v>
+        <v>18.149091</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
@@ -3900,17 +3838,19 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Gold Stream Arrangement -</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr"/>
+          <t>Accounts payable and accrued liabilities 11 8,783,714</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>PayablesAndAccruedExpenses</t>
+        </is>
+      </c>
       <c r="E34" s="5" t="n">
-        <v>1.125775</v>
-      </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.248819</v>
+      </c>
+      <c r="F34" s="5" t="n">
+        <v>20.743438</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
@@ -3931,17 +3871,17 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Provision for reclamation and rehabilitation 12 1,412,917</t>
+          <t>Gold Stream Arrangement -</t>
         </is>
       </c>
       <c r="D35" t="inlineStr"/>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F35" s="5" t="n">
-        <v>3.138574</v>
+      <c r="E35" s="5" t="n">
+        <v>1.125775</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
@@ -3962,19 +3902,17 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Total current liabilities 10,196,631</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>CurrentLiabilities</t>
-        </is>
-      </c>
-      <c r="E36" s="5" t="n">
-        <v>1.374594</v>
+          <t>Provision for reclamation and rehabilitation 12 1,412,917</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr"/>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F36" s="5" t="n">
-        <v>23.882012</v>
+        <v>3.138574</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
@@ -3995,23 +3933,19 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Accounts payable and accrued liabilities 11 869,762</t>
+          <t>Total current liabilities 10,196,631</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>PayablesAndAccruedExpenses</t>
-        </is>
-      </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>CurrentLiabilities</t>
+        </is>
+      </c>
+      <c r="E37" s="5" t="n">
+        <v>1.374594</v>
+      </c>
+      <c r="F37" s="5" t="n">
+        <v>23.882012</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
@@ -4032,17 +3966,23 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Provision for reclamation and rehabilitation 12 722,653</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr"/>
+          <t>Accounts payable and accrued liabilities 11 869,762</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>PayablesAndAccruedExpenses</t>
+        </is>
+      </c>
       <c r="E38" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F38" s="5" t="n">
-        <v>2.090551</v>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
@@ -4063,19 +4003,17 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Total liabilities 11,789,046</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>TotalLiabilities</t>
-        </is>
-      </c>
-      <c r="E39" s="5" t="n">
-        <v>1.374594</v>
+          <t>Provision for reclamation and rehabilitation 12 722,653</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr"/>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F39" s="5" t="n">
-        <v>25.972563</v>
+        <v>2.090551</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
@@ -4091,24 +4029,24 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Shareholders' equity (deficit)</t>
+          <t>Current liabilities</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Share capital 13 70,294,651</t>
+          <t>Total liabilities 11,789,046</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>CapitalStock</t>
+          <t>TotalLiabilities</t>
         </is>
       </c>
       <c r="E40" s="5" t="n">
-        <v>36.055299</v>
+        <v>1.374594</v>
       </c>
       <c r="F40" s="5" t="n">
-        <v>50.07792</v>
+        <v>25.972563</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
@@ -4129,19 +4067,19 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Contributed surplus 7,672,820</t>
+          <t>Share capital 13 70,294,651</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>AdditionalPaidInCapital</t>
+          <t>CapitalStock</t>
         </is>
       </c>
       <c r="E41" s="5" t="n">
-        <v>6.560387</v>
+        <v>36.055299</v>
       </c>
       <c r="F41" s="5" t="n">
-        <v>6.947876</v>
+        <v>50.07792</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
@@ -4162,19 +4100,19 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Accumulated other comprehensive income (loss) 1,577,440</t>
+          <t>Contributed surplus 7,672,820</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>GainsLossesNotAffectingRetainedEarnings</t>
+          <t>AdditionalPaidInCapital</t>
         </is>
       </c>
       <c r="E42" s="5" t="n">
-        <v>0.420913</v>
+        <v>6.560387</v>
       </c>
       <c r="F42" s="5" t="n">
-        <v>-0.633026</v>
+        <v>6.947876</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
@@ -4190,24 +4128,24 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Deficit (73,490,620) (64,216,242) ( 38,987,531)</t>
+          <t>Shareholders' equity (deficit)</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Total shareholders' equity (deficit) 6,054,291</t>
+          <t>Accumulated other comprehensive income (loss) 1,577,440</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>StockholdersEquity</t>
+          <t>GainsLossesNotAffectingRetainedEarnings</t>
         </is>
       </c>
       <c r="E43" s="5" t="n">
-        <v>4.049068</v>
+        <v>0.420913</v>
       </c>
       <c r="F43" s="5" t="n">
-        <v>-7.823472</v>
+        <v>-0.633026</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
@@ -4223,24 +4161,20 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Deficit (73,490,620) (64,216,242) ( 38,987,531)</t>
+          <t>Shareholders' equity (deficit)</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>TOTAL LIABILITIES AND SHAREHOLDERS' EQUITY 17,843,337</t>
-        </is>
-      </c>
-      <c r="D44" t="inlineStr">
-        <is>
-          <t>TotalLiabilitiesAndTotalEquityGrossMinorityInterest</t>
-        </is>
-      </c>
+          <t>Deficit (73,490,620)</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr"/>
       <c r="E44" s="5" t="n">
-        <v>5.423662</v>
+        <v>-38.987531</v>
       </c>
       <c r="F44" s="5" t="n">
-        <v>18.149091</v>
+        <v>-64.21624199999999</v>
       </c>
       <c r="G44" t="inlineStr">
         <is>
@@ -4256,20 +4190,24 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Deficit (73,490,620) (64,216,242) ( 38,987,531)</t>
+          <t>Shareholders' equity (deficit)</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Approved by the Audit Committee of the Board of Directors on November</t>
-        </is>
-      </c>
-      <c r="D45" t="inlineStr"/>
+          <t>Total shareholders' equity (deficit) 6,054,291</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>StockholdersEquity</t>
+        </is>
+      </c>
       <c r="E45" s="5" t="n">
-        <v>0.00202</v>
+        <v>4.049068</v>
       </c>
       <c r="F45" s="5" t="n">
-        <v>2.6e-05</v>
+        <v>-7.823472</v>
       </c>
       <c r="G45" t="inlineStr">
         <is>
@@ -4280,59 +4218,63 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>cash_flow</t>
+          <t>balance_sheet</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>For the eight</t>
+          <t>Shareholders' equity (deficit)</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>December 31, 2020 April</t>
-        </is>
-      </c>
-      <c r="D46" t="inlineStr"/>
-      <c r="E46" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>TOTAL LIABILITIES AND SHAREHOLDERS' EQUITY 17,843,337</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>TotalLiabilitiesAndTotalEquityGrossMinorityInterest</t>
+        </is>
+      </c>
+      <c r="E46" s="5" t="n">
+        <v>5.423662</v>
       </c>
       <c r="F46" s="5" t="n">
-        <v>2.019</v>
-      </c>
-      <c r="G46" s="5" t="n">
-        <v>0.03</v>
+        <v>18.149091</v>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>cash_flow</t>
+          <t>balance_sheet</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>For the eight</t>
+          <t>Shareholders' equity (deficit)</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>December</t>
+          <t>Approved by the Audit Committee of the Board of Directors on November</t>
         </is>
       </c>
       <c r="D47" t="inlineStr"/>
-      <c r="E47" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E47" s="5" t="n">
+        <v>0.00202</v>
       </c>
       <c r="F47" s="5" t="n">
-        <v>2.019</v>
-      </c>
-      <c r="G47" s="5" t="n">
-        <v>0.031</v>
+        <v>2.6e-05</v>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="48">
@@ -4341,14 +4283,10 @@
           <t>cash_flow</t>
         </is>
       </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>Operating activities</t>
-        </is>
-      </c>
+      <c r="B48" t="inlineStr"/>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Net loss for the period $ (12,129) $ (</t>
+          <t>For the eight For the year ended For the year ended Note months ended December 31, 2020 April 30, 2019 December</t>
         </is>
       </c>
       <c r="D48" t="inlineStr"/>
@@ -4358,10 +4296,10 @@
         </is>
       </c>
       <c r="F48" s="5" t="n">
-        <v>-25.227</v>
+        <v>2.019</v>
       </c>
       <c r="G48" s="5" t="n">
-        <v>9.275</v>
+        <v>0.031</v>
       </c>
     </row>
     <row r="49">
@@ -4372,12 +4310,12 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Non-cash items</t>
+          <t>Operating activities</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Accretion expense 21 2 3</t>
+          <t>Net loss for the period $ (12,129) $</t>
         </is>
       </c>
       <c r="D49" t="inlineStr"/>
@@ -4387,10 +4325,10 @@
         </is>
       </c>
       <c r="F49" s="5" t="n">
-        <v>0.005</v>
+        <v>-25.227</v>
       </c>
       <c r="G49" s="5" t="n">
-        <v>0.005</v>
+        <v>-9.275</v>
       </c>
     </row>
     <row r="50">
@@ -4406,24 +4344,20 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Depreciation, depletion and amortization 1 06 7 1</t>
-        </is>
-      </c>
-      <c r="D50" t="inlineStr">
-        <is>
-          <t>DepreciationAmortizationDepletion</t>
-        </is>
-      </c>
+          <t>Accretion expense 21</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr"/>
       <c r="E50" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
       <c r="F50" s="5" t="n">
-        <v>0.005</v>
+        <v>0.055</v>
       </c>
       <c r="G50" s="5" t="n">
-        <v>0.006</v>
+        <v>0.023</v>
       </c>
     </row>
     <row r="51">
@@ -4439,22 +4373,24 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Gain on disposal of equipment ( 861)</t>
-        </is>
-      </c>
-      <c r="D51" t="inlineStr"/>
+          <t>Depreciation, depletion and amortization 106</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E51" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F51" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F51" s="5" t="n">
+        <v>0.065</v>
       </c>
       <c r="G51" s="5" t="n">
-        <v>-0.067</v>
+        <v>0.07099999999999999</v>
       </c>
     </row>
     <row r="52">
@@ -4470,7 +4406,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Loss on disposal of supplies and spare parts 21</t>
+          <t>Change in provision for reclamation and rehabilitation 1,066</t>
         </is>
       </c>
       <c r="D52" t="inlineStr"/>
@@ -4479,15 +4415,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F52" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G52" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F52" s="5" t="n">
+        <v>-0.109</v>
+      </c>
+      <c r="G52" s="5" t="n">
+        <v>-2.275</v>
       </c>
     </row>
     <row r="53">
@@ -4503,7 +4435,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Provision for obsolete supplies and spare parts 4 75</t>
+          <t>Gain on disposal of equipment (861)</t>
         </is>
       </c>
       <c r="D53" t="inlineStr"/>
@@ -4517,10 +4449,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G53" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G53" s="5" t="n">
+        <v>-0.067</v>
       </c>
     </row>
     <row r="54">
@@ -4536,14 +4466,10 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Gain on settlement of accounts payable - (</t>
-        </is>
-      </c>
-      <c r="D54" t="inlineStr">
-        <is>
-          <t>ChangeInPayablesAndAccruedExpense</t>
-        </is>
-      </c>
+          <t>Loss on disposal of supplies and spare parts 21</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr"/>
       <c r="E54" t="inlineStr">
         <is>
           <t>-</t>
@@ -4554,8 +4480,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G54" s="5" t="n">
-        <v>4.754</v>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="55">
@@ -4566,12 +4494,12 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Writedown of inventory - 8 ,617 -</t>
+          <t>Non-cash items</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Interest expense 72 1</t>
+          <t>Provision for obsolete supplies and spare parts 475</t>
         </is>
       </c>
       <c r="D55" t="inlineStr"/>
@@ -4580,11 +4508,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F55" s="5" t="n">
-        <v>0.14</v>
-      </c>
-      <c r="G55" s="5" t="n">
-        <v>0.007</v>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="56">
@@ -4595,17 +4527,17 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Writedown of inventory - 8 ,617 -</t>
+          <t>Non-cash items</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Share-based payments 6 24</t>
+          <t>Gain on settlement of accounts payable -</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>StockBasedCompensation</t>
+          <t>ChangeInPayablesAndAccruedExpense</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -4613,11 +4545,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F56" s="5" t="n">
-        <v>0.395</v>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G56" s="5" t="n">
-        <v>0.657</v>
+        <v>-4.754</v>
       </c>
     </row>
     <row r="57">
@@ -4628,12 +4562,12 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Writedown of inventory - 8 ,617 -</t>
+          <t>Non-cash items</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Extinguishment of gold stream arrangement - -</t>
+          <t>Writedown of inventory -</t>
         </is>
       </c>
       <c r="D57" t="inlineStr"/>
@@ -4642,11 +4576,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F57" s="5" t="n">
-        <v>0.641</v>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G57" s="5" t="n">
-        <v>0.002</v>
+        <v>8.617000000000001</v>
       </c>
     </row>
     <row r="58">
@@ -4657,12 +4593,12 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Investing activities</t>
+          <t>Non-cash items</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Proceeds on sale of equipment 1 ,137</t>
+          <t>Interest expense 72</t>
         </is>
       </c>
       <c r="D58" t="inlineStr"/>
@@ -4671,13 +4607,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F58" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F58" s="5" t="n">
+        <v>0.14</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>0.449</v>
+        <v>0.017</v>
       </c>
     </row>
     <row r="59">
@@ -4688,27 +4622,29 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Investing activities</t>
+          <t>Non-cash items</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Purchase of exploration and evaluation asset - (</t>
-        </is>
-      </c>
-      <c r="D59" t="inlineStr"/>
+          <t>Share-based payments 624</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>StockBasedCompensation</t>
+        </is>
+      </c>
       <c r="E59" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F59" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F59" s="5" t="n">
+        <v>0.395</v>
       </c>
       <c r="G59" s="5" t="n">
-        <v>0.645</v>
+        <v>0.657</v>
       </c>
     </row>
     <row r="60">
@@ -4719,12 +4655,12 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Investing activities</t>
+          <t>Non-cash items</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Net cash used in (funded by) investing activities $ (28,830) $</t>
+          <t>Extinguishment of gold stream arrangement -</t>
         </is>
       </c>
       <c r="D60" t="inlineStr"/>
@@ -4734,10 +4670,12 @@
         </is>
       </c>
       <c r="F60" s="5" t="n">
-        <v>3.202</v>
-      </c>
-      <c r="G60" s="5" t="n">
-        <v>-10.002</v>
+        <v>20.641</v>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="61">
@@ -4748,12 +4686,12 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>share issuance costs of ($885,743)</t>
+          <t>Non-cash items</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Drawdown on term loan 15,000</t>
+          <t>Unrealized foreign exchange loss 869</t>
         </is>
       </c>
       <c r="D61" t="inlineStr"/>
@@ -4762,15 +4700,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F61" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G61" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F61" s="5" t="n">
+        <v>-0.986</v>
+      </c>
+      <c r="G61" s="5" t="n">
+        <v>2.128</v>
       </c>
     </row>
     <row r="62">
@@ -4781,12 +4715,12 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>share issuance costs of ($885,743)</t>
+          <t>Non-cash items</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Proceeds on exercise of options 233</t>
+          <t>Non-cash items total</t>
         </is>
       </c>
       <c r="D62" t="inlineStr"/>
@@ -4795,13 +4729,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F62" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F62" s="5" t="n">
+        <v>-5.026</v>
       </c>
       <c r="G62" s="5" t="n">
-        <v>0.021</v>
+        <v>-4.858</v>
       </c>
     </row>
     <row r="63">
@@ -4812,25 +4744,29 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>share issuance costs of ($885,743)</t>
+          <t>Non-cash items</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Proceeds on exercise of warrants - -</t>
-        </is>
-      </c>
-      <c r="D63" t="inlineStr"/>
+          <t>Changes in non-cash working capital 19 609</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>ChangeInWorkingCapital</t>
+        </is>
+      </c>
       <c r="E63" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
       <c r="F63" s="5" t="n">
-        <v>0.001</v>
+        <v>-1.948</v>
       </c>
       <c r="G63" s="5" t="n">
-        <v>0.001</v>
+        <v>-4.555</v>
       </c>
     </row>
     <row r="64">
@@ -4841,27 +4777,29 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>share issuance costs of ($885,743)</t>
+          <t>Non-cash items</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Interest paid -</t>
-        </is>
-      </c>
-      <c r="D64" t="inlineStr"/>
+          <t>Net cash used in operating activities (9,127)</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>OperatingCashFlow</t>
+        </is>
+      </c>
       <c r="E64" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
       <c r="F64" s="5" t="n">
-        <v>-0.045</v>
-      </c>
-      <c r="G64" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-6.974</v>
+      </c>
+      <c r="G64" s="5" t="n">
+        <v>-9.413</v>
       </c>
     </row>
     <row r="65">
@@ -4872,29 +4810,27 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>share issuance costs of ($885,743)</t>
+          <t>Investing activities</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Net cash provided by financing activates $ 35,295 $ 2</t>
-        </is>
-      </c>
-      <c r="D65" t="inlineStr">
-        <is>
-          <t>FinancingCashFlow</t>
-        </is>
-      </c>
+          <t>Business acquisition, net of inflow of cash -</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr"/>
       <c r="E65" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
       <c r="F65" s="5" t="n">
-        <v>6.375</v>
-      </c>
-      <c r="G65" s="5" t="n">
-        <v>0.205</v>
+        <v>3.315</v>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="66">
@@ -4905,12 +4841,12 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>share issuance costs of ($885,743)</t>
+          <t>Investing activities</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Effect of foreign exchange on cash and cash equivalents 1 ,042</t>
+          <t>Proceeds on sale of equipment 1,137</t>
         </is>
       </c>
       <c r="D66" t="inlineStr"/>
@@ -4919,11 +4855,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F66" s="5" t="n">
-        <v>-0.077</v>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G66" s="5" t="n">
-        <v>0.102</v>
+        <v>0.449</v>
       </c>
     </row>
     <row r="67">
@@ -4934,29 +4872,27 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>share issuance costs of ($885,743)</t>
+          <t>Investing activities</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Change in cash and cash equivalents (1,620)</t>
-        </is>
-      </c>
-      <c r="D67" t="inlineStr">
-        <is>
-          <t>ChangesInCash</t>
-        </is>
-      </c>
+          <t>Purchase of exploration and evaluation asset -</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr"/>
       <c r="E67" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F67" s="5" t="n">
-        <v>2.526</v>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G67" s="5" t="n">
-        <v>0.892</v>
+        <v>-0.645</v>
       </c>
     </row>
     <row r="68">
@@ -4967,29 +4903,25 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>share issuance costs of ($885,743)</t>
+          <t>Investing activities</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Cash and cash equivalents, end of period $ 2 ,633 $</t>
-        </is>
-      </c>
-      <c r="D68" t="inlineStr">
-        <is>
-          <t>EndCashPosition</t>
-        </is>
-      </c>
+          <t>Expenditures on mineral property, plant and equipment (29,967)</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr"/>
       <c r="E68" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
       <c r="F68" s="5" t="n">
-        <v>3.361</v>
+        <v>-0.113</v>
       </c>
       <c r="G68" s="5" t="n">
-        <v>4.253</v>
+        <v>-9.805999999999999</v>
       </c>
     </row>
     <row r="69">
@@ -5000,12 +4932,12 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Operating activities</t>
+          <t>Investing activities</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Net loss for the period $ (9,274,378) $</t>
+          <t>Net cash used in (funded by) investing activities $ (28,830) $</t>
         </is>
       </c>
       <c r="D69" t="inlineStr"/>
@@ -5015,12 +4947,10 @@
         </is>
       </c>
       <c r="F69" s="5" t="n">
-        <v>-25.228711</v>
-      </c>
-      <c r="G69" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>3.202</v>
+      </c>
+      <c r="G69" s="5" t="n">
+        <v>-10.002</v>
       </c>
     </row>
     <row r="70">
@@ -5031,12 +4961,12 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Operating activities</t>
+          <t>Financing activities</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Interest received -</t>
+          <t>Advances from Marlin prior to the acquisition -</t>
         </is>
       </c>
       <c r="D70" t="inlineStr"/>
@@ -5045,10 +4975,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F70" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F70" s="5" t="n">
+        <v>3.037</v>
       </c>
       <c r="G70" t="inlineStr">
         <is>
@@ -5064,12 +4992,12 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Non-cash items</t>
+          <t>20,062              20,184                3,372   share issuance costs of ($885,743)</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Accretion expense 12 23,312</t>
+          <t>Drawdown on term loan 15,000</t>
         </is>
       </c>
       <c r="D71" t="inlineStr"/>
@@ -5078,8 +5006,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F71" s="5" t="n">
-        <v>0.055469</v>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
@@ -5095,12 +5025,12 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Non-cash items</t>
+          <t>20,062              20,184                3,372   share issuance costs of ($885,743)</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Change in provision for reclamation and rehabilitation 12 (2,275,286)</t>
+          <t>Proceeds on exercise of options 233</t>
         </is>
       </c>
       <c r="D72" t="inlineStr"/>
@@ -5109,13 +5039,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F72" s="5" t="n">
-        <v>-0.108704</v>
-      </c>
-      <c r="G72" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G72" s="5" t="n">
+        <v>0.021</v>
       </c>
     </row>
     <row r="73">
@@ -5126,26 +5056,22 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Non-cash items</t>
+          <t>20,062              20,184                3,372   share issuance costs of ($885,743)</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Depreciation, depletion and amortization 71,083</t>
-        </is>
-      </c>
-      <c r="D73" t="inlineStr">
-        <is>
-          <t>DepreciationAmortizationDepletion</t>
-        </is>
-      </c>
+          <t>Proceeds on exercise of warrants -</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr"/>
       <c r="E73" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
       <c r="F73" s="5" t="n">
-        <v>0.064891</v>
+        <v>0.011</v>
       </c>
       <c r="G73" t="inlineStr">
         <is>
@@ -5161,22 +5087,26 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Non-cash items</t>
+          <t>20,062              20,184                3,372   share issuance costs of ($885,743)</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Extinguishment of gold stream arrangement 6 -</t>
-        </is>
-      </c>
-      <c r="D74" t="inlineStr"/>
+          <t>Interest paid -</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>InterestPaidSupplementalData</t>
+        </is>
+      </c>
       <c r="E74" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
       <c r="F74" s="5" t="n">
-        <v>20.641335</v>
+        <v>-0.045</v>
       </c>
       <c r="G74" t="inlineStr">
         <is>
@@ -5192,29 +5122,29 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Non-cash items</t>
+          <t>20,062              20,184                3,372   share issuance costs of ($885,743)</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Gain on disposal of equipment (67,219)</t>
-        </is>
-      </c>
-      <c r="D75" t="inlineStr"/>
+          <t>Net cash provided by financing activates $ 35,295 $</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>FinancingCashFlow</t>
+        </is>
+      </c>
       <c r="E75" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F75" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G75" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F75" s="5" t="n">
+        <v>6.375</v>
+      </c>
+      <c r="G75" s="5" t="n">
+        <v>20.205</v>
       </c>
     </row>
     <row r="76">
@@ -5225,12 +5155,12 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Non-cash items</t>
+          <t>20,062              20,184                3,372   share issuance costs of ($885,743)</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Gain on settlement of accounts payable 11 (4,753,730)</t>
+          <t>Effect of foreign exchange on cash and cash equivalents 1,042</t>
         </is>
       </c>
       <c r="D76" t="inlineStr"/>
@@ -5239,15 +5169,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F76" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G76" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F76" s="5" t="n">
+        <v>-0.077</v>
+      </c>
+      <c r="G76" s="5" t="n">
+        <v>0.102</v>
       </c>
     </row>
     <row r="77">
@@ -5258,27 +5184,29 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Non-cash items</t>
+          <t>20,062              20,184                3,372   share issuance costs of ($885,743)</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Interest expense 17,166</t>
-        </is>
-      </c>
-      <c r="D77" t="inlineStr"/>
+          <t>Change in cash and cash equivalents (1,620)</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>ChangesInCash</t>
+        </is>
+      </c>
       <c r="E77" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
       <c r="F77" s="5" t="n">
-        <v>0.140296</v>
-      </c>
-      <c r="G77" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>2.526</v>
+      </c>
+      <c r="G77" s="5" t="n">
+        <v>0.892</v>
       </c>
     </row>
     <row r="78">
@@ -5289,17 +5217,17 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Non-cash items</t>
+          <t>20,062              20,184                3,372   share issuance costs of ($885,743)</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Share-based payments 657,041</t>
+          <t>Cash and cash equivalents, beginning of period 4,253</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>StockBasedCompensation</t>
+          <t>BeginningCashPosition</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
@@ -5308,12 +5236,10 @@
         </is>
       </c>
       <c r="F78" s="5" t="n">
-        <v>0.394701</v>
-      </c>
-      <c r="G78" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.835</v>
+      </c>
+      <c r="G78" s="5" t="n">
+        <v>3.361</v>
       </c>
     </row>
     <row r="79">
@@ -5324,27 +5250,29 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Non-cash items</t>
+          <t>20,062              20,184                3,372   share issuance costs of ($885,743)</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Unrealized foreign exchange loss 2,127,969</t>
-        </is>
-      </c>
-      <c r="D79" t="inlineStr"/>
+          <t>Cash and cash equivalents, end of period $ 2,633 $</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>EndCashPosition</t>
+        </is>
+      </c>
       <c r="E79" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
       <c r="F79" s="5" t="n">
-        <v>-0.9859599999999999</v>
-      </c>
-      <c r="G79" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>3.361</v>
+      </c>
+      <c r="G79" s="5" t="n">
+        <v>4.253</v>
       </c>
     </row>
     <row r="80">
@@ -5355,12 +5283,12 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Non-cash items</t>
+          <t>Operating activities</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Writedown of inventories 8 8,617,107</t>
+          <t>Net loss for the period $ (9,274,378) $</t>
         </is>
       </c>
       <c r="D80" t="inlineStr"/>
@@ -5369,10 +5297,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F80" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F80" s="5" t="n">
+        <v>-25.228711</v>
       </c>
       <c r="G80" t="inlineStr">
         <is>
@@ -5388,12 +5314,12 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Non-cash items</t>
+          <t>Operating activities</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Non-cash items total</t>
+          <t>Interest received -</t>
         </is>
       </c>
       <c r="D81" t="inlineStr"/>
@@ -5402,8 +5328,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F81" s="5" t="n">
-        <v>5.026683</v>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
@@ -5424,7 +5352,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Changes in non-cash working capital 19 (4,555,223) (</t>
+          <t>Accretion expense 12 23,312</t>
         </is>
       </c>
       <c r="D82" t="inlineStr"/>
@@ -5434,7 +5362,7 @@
         </is>
       </c>
       <c r="F82" s="5" t="n">
-        <v>1.947571</v>
+        <v>0.055469</v>
       </c>
       <c r="G82" t="inlineStr">
         <is>
@@ -5455,7 +5383,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Net cash used in operating activities (9,412,158) (</t>
+          <t>Change in provision for reclamation and rehabilitation 12 (2,275,286)</t>
         </is>
       </c>
       <c r="D83" t="inlineStr"/>
@@ -5465,7 +5393,7 @@
         </is>
       </c>
       <c r="F83" s="5" t="n">
-        <v>6.974254</v>
+        <v>-0.108704</v>
       </c>
       <c r="G83" t="inlineStr">
         <is>
@@ -5481,22 +5409,26 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Investing activities</t>
+          <t>Non-cash items</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Business acquisition, net of inflow of cash 6 -</t>
-        </is>
-      </c>
-      <c r="D84" t="inlineStr"/>
+          <t>Depreciation, depletion and amortization 71,083</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E84" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
       <c r="F84" s="5" t="n">
-        <v>3.314805</v>
+        <v>0.064891</v>
       </c>
       <c r="G84" t="inlineStr">
         <is>
@@ -5512,12 +5444,12 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Investing activities</t>
+          <t>Non-cash items</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Proceeds on sale of equipment 449,288</t>
+          <t>Extinguishment of gold stream arrangement 6 -</t>
         </is>
       </c>
       <c r="D85" t="inlineStr"/>
@@ -5526,10 +5458,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F85" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F85" s="5" t="n">
+        <v>20.641335</v>
       </c>
       <c r="G85" t="inlineStr">
         <is>
@@ -5545,12 +5475,12 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Investing activities</t>
+          <t>Non-cash items</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Purchase of exploration and evaluation asset (645,000)</t>
+          <t>Gain on disposal of equipment (67,219)</t>
         </is>
       </c>
       <c r="D86" t="inlineStr"/>
@@ -5578,12 +5508,12 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Investing activities</t>
+          <t>Non-cash items</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Expenditures on mineral property, plant and equipment (9,806,072)</t>
+          <t>Gain on settlement of accounts payable 11 (4,753,730)</t>
         </is>
       </c>
       <c r="D87" t="inlineStr"/>
@@ -5592,8 +5522,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F87" s="5" t="n">
-        <v>-0.11282</v>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
@@ -5609,12 +5541,12 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Investing activities</t>
+          <t>Non-cash items</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Net cash used in investing activities ( 10,001,784)</t>
+          <t>Interest expense 17,166</t>
         </is>
       </c>
       <c r="D88" t="inlineStr"/>
@@ -5624,7 +5556,7 @@
         </is>
       </c>
       <c r="F88" s="5" t="n">
-        <v>3.201985</v>
+        <v>0.140296</v>
       </c>
       <c r="G88" t="inlineStr">
         <is>
@@ -5640,17 +5572,17 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Financing activities</t>
+          <t>Non-cash items</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Proceeds on issue of shares, net of share issuance costs 20,184,235</t>
+          <t>Share-based payments 657,041</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>NetOtherFinancingCharges</t>
+          <t>StockBasedCompensation</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
@@ -5659,7 +5591,7 @@
         </is>
       </c>
       <c r="F89" s="5" t="n">
-        <v>3.371936</v>
+        <v>0.394701</v>
       </c>
       <c r="G89" t="inlineStr">
         <is>
@@ -5675,12 +5607,12 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Financing activities</t>
+          <t>Non-cash items</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Advances from Marlin prior to the acquisition -</t>
+          <t>Unrealized foreign exchange loss 2,127,969</t>
         </is>
       </c>
       <c r="D90" t="inlineStr"/>
@@ -5690,7 +5622,7 @@
         </is>
       </c>
       <c r="F90" s="5" t="n">
-        <v>3.036745</v>
+        <v>-0.9859599999999999</v>
       </c>
       <c r="G90" t="inlineStr">
         <is>
@@ -5706,12 +5638,12 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Financing activities</t>
+          <t>Non-cash items</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Proceeds on exercise of warrants -</t>
+          <t>Writedown of inventories 8 8,617,107</t>
         </is>
       </c>
       <c r="D91" t="inlineStr"/>
@@ -5720,8 +5652,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F91" s="5" t="n">
-        <v>0.01119</v>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
@@ -5737,12 +5671,12 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Financing activities</t>
+          <t>Non-cash items</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Proceeds on exercise of options 21,138</t>
+          <t>Changes in non-cash working capital 19 (4,555,223)</t>
         </is>
       </c>
       <c r="D92" t="inlineStr"/>
@@ -5751,10 +5685,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F92" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F92" s="5" t="n">
+        <v>-1.947571</v>
       </c>
       <c r="G92" t="inlineStr">
         <is>
@@ -5770,12 +5702,12 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Financing activities</t>
+          <t>Non-cash items</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Interest paid on advances -</t>
+          <t>Net cash used in operating activities (9,412,158)</t>
         </is>
       </c>
       <c r="D93" t="inlineStr"/>
@@ -5785,7 +5717,7 @@
         </is>
       </c>
       <c r="F93" s="5" t="n">
-        <v>-0.044833</v>
+        <v>-6.974254</v>
       </c>
       <c r="G93" t="inlineStr">
         <is>
@@ -5801,26 +5733,22 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Financing activities</t>
+          <t>Investing activities</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Net cash provided by financing activates 20,205,373</t>
-        </is>
-      </c>
-      <c r="D94" t="inlineStr">
-        <is>
-          <t>FinancingCashFlow</t>
-        </is>
-      </c>
+          <t>Business acquisition, net of inflow of cash 6 -</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr"/>
       <c r="E94" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
       <c r="F94" s="5" t="n">
-        <v>6.375038</v>
+        <v>3.314805</v>
       </c>
       <c r="G94" t="inlineStr">
         <is>
@@ -5836,12 +5764,12 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Financing activities</t>
+          <t>Investing activities</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Effect of foreign exchange on cash and cash equivalents 100,623</t>
+          <t>Proceeds on sale of equipment 449,288</t>
         </is>
       </c>
       <c r="D95" t="inlineStr"/>
@@ -5850,8 +5778,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F95" s="5" t="n">
-        <v>-0.076989</v>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
@@ -5867,26 +5797,24 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Financing activities</t>
+          <t>Investing activities</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Change in cash and cash equivalents 892,054</t>
-        </is>
-      </c>
-      <c r="D96" t="inlineStr">
-        <is>
-          <t>ChangesInCash</t>
-        </is>
-      </c>
+          <t>Purchase of exploration and evaluation asset (645,000)</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr"/>
       <c r="E96" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F96" s="5" t="n">
-        <v>2.52578</v>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
@@ -5902,26 +5830,22 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Financing activities</t>
+          <t>Investing activities</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Cash and cash equivalents, beginning of period 3,361,048</t>
-        </is>
-      </c>
-      <c r="D97" t="inlineStr">
-        <is>
-          <t>BeginningCashPosition</t>
-        </is>
-      </c>
+          <t>Expenditures on mineral property, plant and equipment (9,806,072)</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr"/>
       <c r="E97" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
       <c r="F97" s="5" t="n">
-        <v>0.835268</v>
+        <v>-0.11282</v>
       </c>
       <c r="G97" t="inlineStr">
         <is>
@@ -5937,26 +5861,22 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Financing activities</t>
+          <t>Investing activities</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Cash and cash equivalents, end of period $ 4,253,102 $</t>
-        </is>
-      </c>
-      <c r="D98" t="inlineStr">
-        <is>
-          <t>EndCashPosition</t>
-        </is>
-      </c>
+          <t>Net cash used in investing activities (10,001,784)</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr"/>
       <c r="E98" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
       <c r="F98" s="5" t="n">
-        <v>3.361048</v>
+        <v>3.201985</v>
       </c>
       <c r="G98" t="inlineStr">
         <is>
@@ -5967,48 +5887,52 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Production costs ( 21) ( 5,033) ( 11,930)</t>
+          <t>Financing activities</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Writedown of inventories - (</t>
-        </is>
-      </c>
-      <c r="D99" t="inlineStr"/>
+          <t>Proceeds on issue of shares, net of share issuance costs 20,184,235</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>NetOtherFinancingCharges</t>
+        </is>
+      </c>
       <c r="E99" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F99" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G99" s="5" t="n">
-        <v>8.617000000000001</v>
+      <c r="F99" s="5" t="n">
+        <v>3.371936</v>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Other income (expense)</t>
+          <t>Financing activities</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Gain on disposal of equipment 9 07 6</t>
+          <t>Proceeds on exercise of warrants -</t>
         </is>
       </c>
       <c r="D100" t="inlineStr"/>
@@ -6017,29 +5941,29 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F100" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G100" s="5" t="n">
-        <v>0.007</v>
+      <c r="F100" s="5" t="n">
+        <v>0.01119</v>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Other income (expense)</t>
+          <t>Financing activities</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Loss on disposal of supplies and spare parts ( 21)</t>
+          <t>Proceeds on exercise of options 21,138</t>
         </is>
       </c>
       <c r="D101" t="inlineStr"/>
@@ -6062,17 +5986,17 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Other income (expense)</t>
+          <t>Financing activities</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Provision for obsolete supplies and spare parts ( 475)</t>
+          <t>Interest paid on advances -</t>
         </is>
       </c>
       <c r="D102" t="inlineStr"/>
@@ -6081,10 +6005,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F102" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F102" s="5" t="n">
+        <v>-0.044833</v>
       </c>
       <c r="G102" t="inlineStr">
         <is>
@@ -6095,46 +6017,52 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Transaction cost - - ( 518)</t>
+          <t>Financing activities</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Interest income 7 3 5 18</t>
-        </is>
-      </c>
-      <c r="D103" t="inlineStr"/>
+          <t>Net cash provided by financing activates 20,205,373</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>FinancingCashFlow</t>
+        </is>
+      </c>
       <c r="E103" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
       <c r="F103" s="5" t="n">
-        <v>0.095</v>
-      </c>
-      <c r="G103" s="5" t="n">
-        <v>0.006</v>
+        <v>6.375038</v>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Other comprehensive income (loss)</t>
+          <t>Financing activities</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Weighted average common shares outstanding (thousands) 616,941 4</t>
+          <t>Effect of foreign exchange on cash and cash equivalents 100,623</t>
         </is>
       </c>
       <c r="D104" t="inlineStr"/>
@@ -6144,65 +6072,77 @@
         </is>
       </c>
       <c r="F104" s="5" t="n">
-        <v>239.008</v>
-      </c>
-      <c r="G104" s="5" t="n">
-        <v>98.803</v>
+        <v>-0.076989</v>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>income (loss)</t>
+          <t>Financing activities</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Balance at April 30, 2018 192,104 $ 36,056 $ 6 ,560 $ 421 $</t>
-        </is>
-      </c>
-      <c r="D105" t="inlineStr"/>
+          <t>Change in cash and cash equivalents 892,054</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>ChangesInCash</t>
+        </is>
+      </c>
       <c r="E105" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
       <c r="F105" s="5" t="n">
-        <v>4.049</v>
-      </c>
-      <c r="G105" s="5" t="n">
-        <v>-38.988</v>
+        <v>2.52578</v>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>income (loss)</t>
+          <t>Financing activities</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Shares issued on business combination 91,233 10,632 - -</t>
-        </is>
-      </c>
-      <c r="D106" t="inlineStr"/>
+          <t>Cash and cash equivalents, beginning of period 3,361,048</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>BeginningCashPosition</t>
+        </is>
+      </c>
       <c r="E106" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
       <c r="F106" s="5" t="n">
-        <v>10.632</v>
+        <v>0.835268</v>
       </c>
       <c r="G106" t="inlineStr">
         <is>
@@ -6213,27 +6153,31 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>income (loss)</t>
+          <t>Financing activities</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Shares issued on private placement 30,000 3,416 - -</t>
-        </is>
-      </c>
-      <c r="D107" t="inlineStr"/>
+          <t>Cash and cash equivalents, end of period $ 4,253,102 $</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>EndCashPosition</t>
+        </is>
+      </c>
       <c r="E107" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
       <c r="F107" s="5" t="n">
-        <v>3.416</v>
+        <v>3.361048</v>
       </c>
       <c r="G107" t="inlineStr">
         <is>
@@ -6247,29 +6191,27 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B108" t="inlineStr">
-        <is>
-          <t>income (loss)</t>
-        </is>
-      </c>
+      <c r="B108" t="inlineStr"/>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Shares issued on exercise of warrants 67 11 - -</t>
-        </is>
-      </c>
-      <c r="D108" t="inlineStr"/>
+          <t>Revenue $ 1,398 $</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>TotalRevenue</t>
+        </is>
+      </c>
       <c r="E108" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
       <c r="F108" s="5" t="n">
-        <v>0.011</v>
-      </c>
-      <c r="G108" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>7.931</v>
+      </c>
+      <c r="G108" s="5" t="n">
+        <v>8.583</v>
       </c>
     </row>
     <row r="109">
@@ -6280,12 +6222,12 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>income (loss)</t>
+          <t>Cost of sales</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Transfer of warrant value - 7 (7) -</t>
+          <t>Production costs (21)</t>
         </is>
       </c>
       <c r="D109" t="inlineStr"/>
@@ -6294,15 +6236,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F109" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G109" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F109" s="5" t="n">
+        <v>-11.93</v>
+      </c>
+      <c r="G109" s="5" t="n">
+        <v>-5.033</v>
       </c>
     </row>
     <row r="110">
@@ -6313,12 +6251,12 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>income (loss)</t>
+          <t>Cost of sales</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Share-based compensation - - 3 95 -</t>
+          <t>Change in inventories (558)</t>
         </is>
       </c>
       <c r="D110" t="inlineStr"/>
@@ -6328,12 +6266,10 @@
         </is>
       </c>
       <c r="F110" s="5" t="n">
-        <v>0.395</v>
-      </c>
-      <c r="G110" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>1.892</v>
+      </c>
+      <c r="G110" s="5" t="n">
+        <v>-0.946</v>
       </c>
     </row>
     <row r="111">
@@ -6344,12 +6280,12 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>income (loss)</t>
+          <t>Cost of sales</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Shares issued on rights offering 270,017 20,385 - -</t>
+          <t>Writedown of inventories -</t>
         </is>
       </c>
       <c r="D111" t="inlineStr"/>
@@ -6358,13 +6294,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F111" s="5" t="n">
-        <v>20.385</v>
-      </c>
-      <c r="G111" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G111" s="5" t="n">
+        <v>-8.617000000000001</v>
       </c>
     </row>
     <row r="112">
@@ -6375,27 +6311,29 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>income (loss)</t>
+          <t>Cost of sales</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Shares issued on exercise of options 280 21 - -</t>
-        </is>
-      </c>
-      <c r="D112" t="inlineStr"/>
+          <t>Depreciation, depletion and amortization (91)</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E112" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
       <c r="F112" s="5" t="n">
-        <v>0.021</v>
-      </c>
-      <c r="G112" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.042</v>
+      </c>
+      <c r="G112" s="5" t="n">
+        <v>0.061</v>
       </c>
     </row>
     <row r="113">
@@ -6406,12 +6344,12 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>income (loss)</t>
+          <t>Cost of sales</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Transfer of option value - 11 (11) -</t>
+          <t>Cost of sales total</t>
         </is>
       </c>
       <c r="D113" t="inlineStr"/>
@@ -6420,15 +6358,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F113" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G113" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F113" s="5" t="n">
+        <v>-10.08</v>
+      </c>
+      <c r="G113" s="5" t="n">
+        <v>-14.657</v>
       </c>
     </row>
     <row r="114">
@@ -6439,12 +6373,12 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>income (loss)</t>
+          <t>Cost of sales</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Share-based compensation - - 7 36 -</t>
+          <t>Gross (loss) income 728</t>
         </is>
       </c>
       <c r="D114" t="inlineStr"/>
@@ -6454,12 +6388,10 @@
         </is>
       </c>
       <c r="F114" s="5" t="n">
-        <v>0.736</v>
-      </c>
-      <c r="G114" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-2.149</v>
+      </c>
+      <c r="G114" s="5" t="n">
+        <v>-6.074</v>
       </c>
     </row>
     <row r="115">
@@ -6470,12 +6402,12 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>income (loss)</t>
+          <t>Cost of sales</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Other comprehensive income - - - 2,210</t>
+          <t>Exploration and evaluation expenses (5,227)</t>
         </is>
       </c>
       <c r="D115" t="inlineStr"/>
@@ -6485,12 +6417,10 @@
         </is>
       </c>
       <c r="F115" s="5" t="n">
-        <v>2.21</v>
-      </c>
-      <c r="G115" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-3.541</v>
+      </c>
+      <c r="G115" s="5" t="n">
+        <v>-4.178</v>
       </c>
     </row>
     <row r="116">
@@ -6501,12 +6431,12 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>income (loss)</t>
+          <t>Cost of sales</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Balance at December 31, 2019 583,701 $ 70,295 $ 7 ,673 $ 1,577 $</t>
+          <t>General and administrative expenses 17 (5,320)</t>
         </is>
       </c>
       <c r="D116" t="inlineStr"/>
@@ -6516,10 +6446,10 @@
         </is>
       </c>
       <c r="F116" s="5" t="n">
-        <v>6.054</v>
+        <v>-2.282</v>
       </c>
       <c r="G116" s="5" t="n">
-        <v>-73.491</v>
+        <v>-2.913</v>
       </c>
     </row>
     <row r="117">
@@ -6530,12 +6460,12 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Shares issued on units private</t>
+          <t>Other income (expense)</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Shares issued on units private placement 71,000 17,453 - -</t>
+          <t>Accretion and interest expense (104)</t>
         </is>
       </c>
       <c r="D117" t="inlineStr"/>
@@ -6545,12 +6475,10 @@
         </is>
       </c>
       <c r="F117" s="5" t="n">
-        <v>17.453</v>
-      </c>
-      <c r="G117" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.176</v>
+      </c>
+      <c r="G117" s="5" t="n">
+        <v>-0.04</v>
       </c>
     </row>
     <row r="118">
@@ -6561,12 +6489,12 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Shares issued on units private</t>
+          <t>Other income (expense)</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Fair value of warrants - - 3 ,494 -</t>
+          <t>Change in provision for reclamation and rehabilitation 10 (1,066)</t>
         </is>
       </c>
       <c r="D118" t="inlineStr"/>
@@ -6575,13 +6503,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F118" s="5" t="n">
-        <v>3.494</v>
-      </c>
-      <c r="G118" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G118" s="5" t="n">
+        <v>2.275</v>
       </c>
     </row>
     <row r="119">
@@ -6592,12 +6520,12 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Shares issued on units private</t>
+          <t>Other income (expense)</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Shares issued on exercise of options 1,430 399 (167) -</t>
+          <t>Extinguishment of gold stream arrangement -</t>
         </is>
       </c>
       <c r="D119" t="inlineStr"/>
@@ -6607,7 +6535,7 @@
         </is>
       </c>
       <c r="F119" s="5" t="n">
-        <v>0.232</v>
+        <v>-20.641</v>
       </c>
       <c r="G119" t="inlineStr">
         <is>
@@ -6623,12 +6551,12 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Shares issued on units private</t>
+          <t>Other income (expense)</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Share-based compensation - - 6 34 -</t>
+          <t>Gain on disposal of equipment 907</t>
         </is>
       </c>
       <c r="D120" t="inlineStr"/>
@@ -6637,13 +6565,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F120" s="5" t="n">
-        <v>0.634</v>
-      </c>
-      <c r="G120" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G120" s="5" t="n">
+        <v>0.067</v>
       </c>
     </row>
     <row r="121">
@@ -6654,12 +6582,12 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Shares issued on units private</t>
+          <t>Other income (expense)</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Other comprehensive income - - - 2,057</t>
+          <t>Loss on disposal of supplies and spare parts (21)</t>
         </is>
       </c>
       <c r="D121" t="inlineStr"/>
@@ -6668,8 +6596,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F121" s="5" t="n">
-        <v>2.057</v>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
@@ -6685,12 +6615,12 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Shares issued on units private</t>
+          <t>Other income (expense)</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Balance at December 31, 2020 656,131 $ 87,262 $ 1 1,634 $ 3,634 $</t>
+          <t>Provision for obsolete supplies and spare parts (475)</t>
         </is>
       </c>
       <c r="D122" t="inlineStr"/>
@@ -6699,11 +6629,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F122" s="5" t="n">
-        <v>16.91</v>
-      </c>
-      <c r="G122" s="5" t="n">
-        <v>-85.62</v>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="123">
@@ -6714,12 +6648,12 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Note</t>
+          <t>Other income (expense)</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Restated - Note 3 Restated - Note</t>
+          <t>Gain on settlement of accounts payable -</t>
         </is>
       </c>
       <c r="D123" t="inlineStr"/>
@@ -6728,13 +6662,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F123" s="5" t="n">
-        <v>3e-06</v>
-      </c>
-      <c r="G123" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G123" s="5" t="n">
+        <v>4.754</v>
       </c>
     </row>
     <row r="124">
@@ -6745,31 +6679,25 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Note</t>
+          <t>Other income (expense)</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Revenue $ 8,583,218 $</t>
-        </is>
-      </c>
-      <c r="D124" t="inlineStr">
-        <is>
-          <t>TotalRevenue</t>
-        </is>
-      </c>
+          <t>Foreign exchange gain (loss) (1,576)</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr"/>
       <c r="E124" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
       <c r="F124" s="5" t="n">
-        <v>7.931102</v>
-      </c>
-      <c r="G124" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>3.46</v>
+      </c>
+      <c r="G124" s="5" t="n">
+        <v>-3.616</v>
       </c>
     </row>
     <row r="125">
@@ -6780,12 +6708,12 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Cost of sales</t>
+          <t>Other income (expense)</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Production costs (5,032,966)</t>
+          <t>Transaction cost -</t>
         </is>
       </c>
       <c r="D125" t="inlineStr"/>
@@ -6795,7 +6723,7 @@
         </is>
       </c>
       <c r="F125" s="5" t="n">
-        <v>-11.930067</v>
+        <v>-0.518</v>
       </c>
       <c r="G125" t="inlineStr">
         <is>
@@ -6811,27 +6739,29 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Cost of sales</t>
+          <t>Other income (expense)</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Change in inventories (945,657)</t>
-        </is>
-      </c>
-      <c r="D126" t="inlineStr"/>
+          <t>Interest income 73</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>InterestIncome</t>
+        </is>
+      </c>
       <c r="E126" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
       <c r="F126" s="5" t="n">
-        <v>1.892243</v>
-      </c>
-      <c r="G126" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.695</v>
+      </c>
+      <c r="G126" s="5" t="n">
+        <v>0.518</v>
       </c>
     </row>
     <row r="127">
@@ -6842,12 +6772,12 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Cost of sales</t>
+          <t>Other income (expense)</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Writedown of inventories 8 (8,617,107)</t>
+          <t>Loss before income taxes (12,081)</t>
         </is>
       </c>
       <c r="D127" t="inlineStr"/>
@@ -6856,15 +6786,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F127" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G127" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F127" s="5" t="n">
+        <v>-25.152</v>
+      </c>
+      <c r="G127" s="5" t="n">
+        <v>-9.207000000000001</v>
       </c>
     </row>
     <row r="128">
@@ -6875,17 +6801,17 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Cost of sales</t>
+          <t>Other income (expense)</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Depreciation, depletion and amortization (61,196)</t>
+          <t>Income tax expense (48)</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>DepreciationAmortizationDepletion</t>
+          <t>TaxProvision</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
@@ -6894,12 +6820,10 @@
         </is>
       </c>
       <c r="F128" s="5" t="n">
-        <v>-0.041939</v>
-      </c>
-      <c r="G128" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.075</v>
+      </c>
+      <c r="G128" s="5" t="n">
+        <v>-0.068</v>
       </c>
     </row>
     <row r="129">
@@ -6910,12 +6834,12 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Cost of sales</t>
+          <t>Other income (expense)</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Cost of sales total</t>
+          <t>Loss for the period $ (12,129) $</t>
         </is>
       </c>
       <c r="D129" t="inlineStr"/>
@@ -6925,12 +6849,10 @@
         </is>
       </c>
       <c r="F129" s="5" t="n">
-        <v>-10.079763</v>
-      </c>
-      <c r="G129" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-25.227</v>
+      </c>
+      <c r="G129" s="5" t="n">
+        <v>-9.275</v>
       </c>
     </row>
     <row r="130">
@@ -6941,12 +6863,12 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Cost of sales</t>
+          <t>Other comprehensive income (loss)</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Gross loss (6,073,708)</t>
+          <t>Loss for the period (12,129)</t>
         </is>
       </c>
       <c r="D130" t="inlineStr"/>
@@ -6956,12 +6878,10 @@
         </is>
       </c>
       <c r="F130" s="5" t="n">
-        <v>-2.148661</v>
-      </c>
-      <c r="G130" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-25.227</v>
+      </c>
+      <c r="G130" s="5" t="n">
+        <v>-9.275</v>
       </c>
     </row>
     <row r="131">
@@ -6972,12 +6892,12 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Cost of sales</t>
+          <t>Other comprehensive income (loss)</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Exploration and evaluation expenses (4,177,925)</t>
+          <t>Foreign currency translation adjustment 2,057</t>
         </is>
       </c>
       <c r="D131" t="inlineStr"/>
@@ -6987,12 +6907,10 @@
         </is>
       </c>
       <c r="F131" s="5" t="n">
-        <v>-3.541044</v>
-      </c>
-      <c r="G131" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-1.054</v>
+      </c>
+      <c r="G131" s="5" t="n">
+        <v>2.21</v>
       </c>
     </row>
     <row r="132">
@@ -7003,12 +6921,12 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Cost of sales</t>
+          <t>Other comprehensive income (loss)</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>General and administrative expenses (2,912,663)</t>
+          <t>Other comprehensive income for the period 2,057</t>
         </is>
       </c>
       <c r="D132" t="inlineStr"/>
@@ -7018,12 +6936,10 @@
         </is>
       </c>
       <c r="F132" s="5" t="n">
-        <v>-2.282411</v>
-      </c>
-      <c r="G132" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-1.054</v>
+      </c>
+      <c r="G132" s="5" t="n">
+        <v>2.21</v>
       </c>
     </row>
     <row r="133">
@@ -7034,12 +6950,12 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Other income (expense)</t>
+          <t>Other comprehensive income (loss)</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Accretion and interest expense (40,478)</t>
+          <t>Comprehensive loss for the period $ (10,072) $</t>
         </is>
       </c>
       <c r="D133" t="inlineStr"/>
@@ -7049,12 +6965,10 @@
         </is>
       </c>
       <c r="F133" s="5" t="n">
-        <v>-0.176405</v>
-      </c>
-      <c r="G133" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-26.281</v>
+      </c>
+      <c r="G133" s="5" t="n">
+        <v>-7.065</v>
       </c>
     </row>
     <row r="134">
@@ -7065,12 +6979,12 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Other income (expense)</t>
+          <t>Other comprehensive income (loss)</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Gain on settlement of accounts payable 11 4,753,730</t>
+          <t>Basic and diluted loss per common share $ (0.02) $</t>
         </is>
       </c>
       <c r="D134" t="inlineStr"/>
@@ -7079,15 +6993,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F134" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G134" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F134" s="5" t="n">
+        <v>-1.1e-07</v>
+      </c>
+      <c r="G134" s="5" t="n">
+        <v>-2e-08</v>
       </c>
     </row>
     <row r="135">
@@ -7098,12 +7008,12 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Other income (expense)</t>
+          <t>Other comprehensive income (loss)</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Gain on change in provision for reclamation and rehabilitation 12 2,275,286</t>
+          <t>Weighted average common shares outstanding (thousands) 616,941</t>
         </is>
       </c>
       <c r="D135" t="inlineStr"/>
@@ -7112,15 +7022,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F135" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G135" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F135" s="5" t="n">
+        <v>239.008</v>
+      </c>
+      <c r="G135" s="5" t="n">
+        <v>498.803</v>
       </c>
     </row>
     <row r="136">
@@ -7131,12 +7037,12 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Other income (expense)</t>
+          <t>(000s)                                                                        income (loss)</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Gain on disposal of equipment 67,219</t>
+          <t>Balance at April 30, 2018 192,104 $ 36,056 $ 6,560 $ 421 $</t>
         </is>
       </c>
       <c r="D136" t="inlineStr"/>
@@ -7145,15 +7051,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F136" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G136" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F136" s="5" t="n">
+        <v>4.049</v>
+      </c>
+      <c r="G136" s="5" t="n">
+        <v>-38.988</v>
       </c>
     </row>
     <row r="137">
@@ -7164,12 +7066,12 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Other income (expense)</t>
+          <t>(000s)                                                                        income (loss)</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Extinguishment of gold stream arrangement 6 -</t>
+          <t>Shares issued on business combination 91,233 10,632 - -</t>
         </is>
       </c>
       <c r="D137" t="inlineStr"/>
@@ -7179,7 +7081,7 @@
         </is>
       </c>
       <c r="F137" s="5" t="n">
-        <v>-20.641335</v>
+        <v>10.632</v>
       </c>
       <c r="G137" t="inlineStr">
         <is>
@@ -7195,12 +7097,12 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Other income (expense)</t>
+          <t>(000s)                                                                        income (loss)</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Transaction costs -</t>
+          <t>Shares issued on private placement 30,000 3,416 - -</t>
         </is>
       </c>
       <c r="D138" t="inlineStr"/>
@@ -7210,7 +7112,7 @@
         </is>
       </c>
       <c r="F138" s="5" t="n">
-        <v>-0.518397</v>
+        <v>3.416</v>
       </c>
       <c r="G138" t="inlineStr">
         <is>
@@ -7226,12 +7128,12 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Other income (expense)</t>
+          <t>(000s)                                                                        income (loss)</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Foreign exchange loss (3,615,796)</t>
+          <t>Share issue costs - (44) - -</t>
         </is>
       </c>
       <c r="D139" t="inlineStr"/>
@@ -7241,7 +7143,7 @@
         </is>
       </c>
       <c r="F139" s="5" t="n">
-        <v>3.459907</v>
+        <v>-0.044</v>
       </c>
       <c r="G139" t="inlineStr">
         <is>
@@ -7257,26 +7159,22 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Other income (expense)</t>
+          <t>(000s)                                                                        income (loss)</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Interest income 517,681</t>
-        </is>
-      </c>
-      <c r="D140" t="inlineStr">
-        <is>
-          <t>InterestIncome</t>
-        </is>
-      </c>
+          <t>Shares issued on exercise of warrants 67 11 - -</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr"/>
       <c r="E140" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
       <c r="F140" s="5" t="n">
-        <v>0.694931</v>
+        <v>0.011</v>
       </c>
       <c r="G140" t="inlineStr">
         <is>
@@ -7292,12 +7190,12 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Other income (expense)</t>
+          <t>(000s)                                                                        income (loss)</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Loss before income taxes (9,206,654)</t>
+          <t>Transfer of warrant value - 7 (7) -</t>
         </is>
       </c>
       <c r="D141" t="inlineStr"/>
@@ -7306,8 +7204,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F141" s="5" t="n">
-        <v>-25.153415</v>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
@@ -7323,12 +7223,12 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Other income (expense)</t>
+          <t>(000s)                                                                        income (loss)</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Income tax expense 16 (67,724)</t>
+          <t>Share-based compensation - - 395 -</t>
         </is>
       </c>
       <c r="D142" t="inlineStr"/>
@@ -7338,7 +7238,7 @@
         </is>
       </c>
       <c r="F142" s="5" t="n">
-        <v>-0.075296</v>
+        <v>0.395</v>
       </c>
       <c r="G142" t="inlineStr">
         <is>
@@ -7354,27 +7254,29 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Other income (expense)</t>
+          <t>(000s)                                                                        income (loss)</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Loss for the period $ (9,274,378) $</t>
-        </is>
-      </c>
-      <c r="D143" t="inlineStr"/>
+          <t>Net loss - - - -</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
       <c r="E143" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
       <c r="F143" s="5" t="n">
-        <v>-25.228711</v>
-      </c>
-      <c r="G143" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-25.229</v>
+      </c>
+      <c r="G143" s="5" t="n">
+        <v>-25.229</v>
       </c>
     </row>
     <row r="144">
@@ -7385,12 +7287,12 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>Other comprehensive income (loss)</t>
+          <t>(000s)                                                                        income (loss)</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Loss for the period (9,274,378)</t>
+          <t>Other comprehensive loss - - - (1,054)</t>
         </is>
       </c>
       <c r="D144" t="inlineStr"/>
@@ -7400,7 +7302,7 @@
         </is>
       </c>
       <c r="F144" s="5" t="n">
-        <v>-25.228711</v>
+        <v>-1.054</v>
       </c>
       <c r="G144" t="inlineStr">
         <is>
@@ -7416,12 +7318,12 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>Other comprehensive income (loss)</t>
+          <t>(000s)                                                                        income (loss)</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Foreign currency translation adjustment 2,210,466</t>
+          <t>Balance at April 30, 2019 313,404 $ 50,078 $ 6,948 $ (633) $</t>
         </is>
       </c>
       <c r="D145" t="inlineStr"/>
@@ -7431,12 +7333,10 @@
         </is>
       </c>
       <c r="F145" s="5" t="n">
-        <v>-1.053939</v>
-      </c>
-      <c r="G145" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-7.824</v>
+      </c>
+      <c r="G145" s="5" t="n">
+        <v>-64.217</v>
       </c>
     </row>
     <row r="146">
@@ -7447,26 +7347,22 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>Other comprehensive income (loss)</t>
+          <t>(000s)                                                                        income (loss)</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Other comprehensive income (loss) for the period 2,210,466</t>
-        </is>
-      </c>
-      <c r="D146" t="inlineStr">
-        <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
+          <t>Shares issued on rights offering 270,017 20,385 - -</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr"/>
       <c r="E146" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
       <c r="F146" s="5" t="n">
-        <v>-1.053939</v>
+        <v>20.385</v>
       </c>
       <c r="G146" t="inlineStr">
         <is>
@@ -7482,12 +7378,12 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>Other comprehensive income (loss)</t>
+          <t>(000s)                                                                        income (loss)</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Comprehensive loss for the period $ (7,063,912) $</t>
+          <t>Share issue costs - (200) - -</t>
         </is>
       </c>
       <c r="D147" t="inlineStr"/>
@@ -7497,7 +7393,7 @@
         </is>
       </c>
       <c r="F147" s="5" t="n">
-        <v>-26.28265</v>
+        <v>-0.2</v>
       </c>
       <c r="G147" t="inlineStr">
         <is>
@@ -7513,12 +7409,12 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>Other comprehensive income (loss)</t>
+          <t>(000s)                                                                        income (loss)</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Basic and diluted loss per common share $ (0.02) $</t>
+          <t>Shares issued on exercise of options 280 21 - -</t>
         </is>
       </c>
       <c r="D148" t="inlineStr"/>
@@ -7528,7 +7424,7 @@
         </is>
       </c>
       <c r="F148" s="5" t="n">
-        <v>-1.1e-07</v>
+        <v>0.021</v>
       </c>
       <c r="G148" t="inlineStr">
         <is>
@@ -7544,26 +7440,24 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>Other comprehensive income (loss)</t>
+          <t>(000s)                                                                        income (loss)</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Weighted average common shares outstanding 498,802,983</t>
-        </is>
-      </c>
-      <c r="D149" t="inlineStr">
-        <is>
-          <t>SharesOutstanding</t>
-        </is>
-      </c>
+          <t>Transfer of option value - 11 (11) -</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr"/>
       <c r="E149" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F149" s="5" t="n">
-        <v>239.008432</v>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
@@ -7579,12 +7473,12 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>shares surplus comprehensive</t>
+          <t>(000s)                                                                        income (loss)</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Note</t>
+          <t>Share-based compensation - - 736 -</t>
         </is>
       </c>
       <c r="D150" t="inlineStr"/>
@@ -7594,7 +7488,7 @@
         </is>
       </c>
       <c r="F150" s="5" t="n">
-        <v>3e-06</v>
+        <v>0.736</v>
       </c>
       <c r="G150" t="inlineStr">
         <is>
@@ -7610,12 +7504,12 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>income (loss)</t>
+          <t>(000s)                                                                        income (loss)</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Shares issued on exercise of warrants 21,718 6,163 (2,425) - -</t>
+          <t>Other comprehensive income - - - 2,210</t>
         </is>
       </c>
       <c r="D151" t="inlineStr"/>
@@ -7625,7 +7519,7 @@
         </is>
       </c>
       <c r="F151" s="5" t="n">
-        <v>0.003738</v>
+        <v>2.21</v>
       </c>
       <c r="G151" t="inlineStr">
         <is>
@@ -7641,12 +7535,12 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>income (loss)</t>
+          <t>(000s)                                                                        income (loss)</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Shares issued on exercise of options 86,306 23,696 (9,858) - - 1</t>
+          <t>Balance at December 31, 2019 583,701 $ 70,295 $ 7,673 $ 1,577 $</t>
         </is>
       </c>
       <c r="D152" t="inlineStr"/>
@@ -7656,12 +7550,10 @@
         </is>
       </c>
       <c r="F152" s="5" t="n">
-        <v>0.003838</v>
-      </c>
-      <c r="G152" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>6.054</v>
+      </c>
+      <c r="G152" s="5" t="n">
+        <v>-73.491</v>
       </c>
     </row>
     <row r="153">
@@ -7672,12 +7564,12 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>income (loss)</t>
+          <t>Shares issued on units private</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Share issue costs - (212) - - -</t>
+          <t>Shares issued on units private placement 71,000 17,453 - -</t>
         </is>
       </c>
       <c r="D153" t="inlineStr"/>
@@ -7687,7 +7579,7 @@
         </is>
       </c>
       <c r="F153" s="5" t="n">
-        <v>-0.000212</v>
+        <v>17.453</v>
       </c>
       <c r="G153" t="inlineStr">
         <is>
@@ -7703,12 +7595,12 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>income (loss)</t>
+          <t>Shares issued on units private</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Share-based compensation - - 152,402 - -</t>
+          <t>Share issue costs - (885) - -</t>
         </is>
       </c>
       <c r="D154" t="inlineStr"/>
@@ -7718,7 +7610,7 @@
         </is>
       </c>
       <c r="F154" s="5" t="n">
-        <v>0.152402</v>
+        <v>-0.885</v>
       </c>
       <c r="G154" t="inlineStr">
         <is>
@@ -7734,12 +7626,12 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>income (loss)</t>
+          <t>Shares issued on units private</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Net loss - - - - (3,069,964)</t>
+          <t>Fair value of warrants - - 3,494 -</t>
         </is>
       </c>
       <c r="D155" t="inlineStr"/>
@@ -7749,7 +7641,7 @@
         </is>
       </c>
       <c r="F155" s="5" t="n">
-        <v>-3.069964</v>
+        <v>3.494</v>
       </c>
       <c r="G155" t="inlineStr">
         <is>
@@ -7765,12 +7657,12 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>income (loss)</t>
+          <t>Shares issued on units private</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Other comprehensive loss - - - (1,559,530) -</t>
+          <t>Shares issued on exercise of options 1,430 399 (167) -</t>
         </is>
       </c>
       <c r="D156" t="inlineStr"/>
@@ -7780,7 +7672,7 @@
         </is>
       </c>
       <c r="F156" s="5" t="n">
-        <v>-1.55953</v>
+        <v>0.232</v>
       </c>
       <c r="G156" t="inlineStr">
         <is>
@@ -7796,12 +7688,12 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>income (loss)</t>
+          <t>Shares issued on units private</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Shares issued on business combination 9 1,233,386 10,632,283 - - -</t>
+          <t>Share-based compensation - - 634 -</t>
         </is>
       </c>
       <c r="D157" t="inlineStr"/>
@@ -7811,7 +7703,7 @@
         </is>
       </c>
       <c r="F157" s="5" t="n">
-        <v>10.632283</v>
+        <v>0.634</v>
       </c>
       <c r="G157" t="inlineStr">
         <is>
@@ -7827,27 +7719,29 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>income (loss)</t>
+          <t>Shares issued on units private</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Shares issued on private placement 3 0,000,000 3,416,338 - - -</t>
-        </is>
-      </c>
-      <c r="D158" t="inlineStr"/>
+          <t>Net loss - - - -</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
       <c r="E158" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
       <c r="F158" s="5" t="n">
-        <v>3.416338</v>
-      </c>
-      <c r="G158" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-12.129</v>
+      </c>
+      <c r="G158" s="5" t="n">
+        <v>-12.129</v>
       </c>
     </row>
     <row r="159">
@@ -7858,12 +7752,12 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>income (loss)</t>
+          <t>Shares issued on units private</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Share issue costs - ( 44,402) - - -</t>
+          <t>Other comprehensive income - - - 2,057</t>
         </is>
       </c>
       <c r="D159" t="inlineStr"/>
@@ -7873,7 +7767,7 @@
         </is>
       </c>
       <c r="F159" s="5" t="n">
-        <v>-0.044402</v>
+        <v>2.057</v>
       </c>
       <c r="G159" t="inlineStr">
         <is>
@@ -7889,12 +7783,12 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>income (loss)</t>
+          <t>Shares issued on units private</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Shares issued on exercise of warrants 67,000 11,190 - - -</t>
+          <t>Balance at December 31, 2020 656,131 $ 87,262 $ 11,634 $ 3,634 $</t>
         </is>
       </c>
       <c r="D160" t="inlineStr"/>
@@ -7904,12 +7798,10 @@
         </is>
       </c>
       <c r="F160" s="5" t="n">
-        <v>0.01119</v>
-      </c>
-      <c r="G160" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>16.91</v>
+      </c>
+      <c r="G160" s="5" t="n">
+        <v>-85.62</v>
       </c>
     </row>
     <row r="161">
@@ -7920,12 +7812,12 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>income (loss)</t>
+          <t>For the eight</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Transfer of warrant value - 7,212 (7,212) - -</t>
+          <t>Restated - Note 3 Restated - Note</t>
         </is>
       </c>
       <c r="D161" t="inlineStr"/>
@@ -7934,10 +7826,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F161" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F161" s="5" t="n">
+        <v>3e-06</v>
       </c>
       <c r="G161" t="inlineStr">
         <is>
@@ -7953,22 +7843,26 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>income (loss)</t>
+          <t>For the eight</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Share-based compensation - - 3 94,701 - -</t>
-        </is>
-      </c>
-      <c r="D162" t="inlineStr"/>
+          <t>Revenue $ 8,583,218 $</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>TotalRevenue</t>
+        </is>
+      </c>
       <c r="E162" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
       <c r="F162" s="5" t="n">
-        <v>0.394701</v>
+        <v>7.931102</v>
       </c>
       <c r="G162" t="inlineStr">
         <is>
@@ -7984,12 +7878,12 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>income (loss)</t>
+          <t>Cost of sales</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Net loss - - - - ( 25,228,711)</t>
+          <t>Production costs (5,032,966)</t>
         </is>
       </c>
       <c r="D163" t="inlineStr"/>
@@ -7999,7 +7893,7 @@
         </is>
       </c>
       <c r="F163" s="5" t="n">
-        <v>-25.228711</v>
+        <v>-11.930067</v>
       </c>
       <c r="G163" t="inlineStr">
         <is>
@@ -8015,12 +7909,12 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>income (loss)</t>
+          <t>Cost of sales</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Other comprehensive loss - - - (1,053,939) -</t>
+          <t>Change in inventories (945,657)</t>
         </is>
       </c>
       <c r="D164" t="inlineStr"/>
@@ -8030,7 +7924,7 @@
         </is>
       </c>
       <c r="F164" s="5" t="n">
-        <v>-1.053939</v>
+        <v>1.892243</v>
       </c>
       <c r="G164" t="inlineStr">
         <is>
@@ -8046,12 +7940,12 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>income (loss)</t>
+          <t>Cost of sales</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Balance at April 30, 2019 313,404,306 $ 50,077,920 $ 6,947,876 $ (633,026)$ ( 64,216,242)$</t>
+          <t>Writedown of inventories 8 (8,617,107)</t>
         </is>
       </c>
       <c r="D165" t="inlineStr"/>
@@ -8060,8 +7954,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F165" s="5" t="n">
-        <v>-7.823472</v>
+      <c r="F165" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
@@ -8077,22 +7973,26 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>income (loss)</t>
+          <t>Cost of sales</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Shares issued on rights offering 270,017,178 20,384,809 - - -</t>
-        </is>
-      </c>
-      <c r="D166" t="inlineStr"/>
+          <t>Depreciation, depletion and amortization (61,196)</t>
+        </is>
+      </c>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E166" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
       <c r="F166" s="5" t="n">
-        <v>20.384809</v>
+        <v>0.041939</v>
       </c>
       <c r="G166" t="inlineStr">
         <is>
@@ -8108,12 +8008,12 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>income (loss)</t>
+          <t>Cost of sales</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Share issue costs - (200,574) - - -</t>
+          <t>Gross loss (6,073,708)</t>
         </is>
       </c>
       <c r="D167" t="inlineStr"/>
@@ -8123,7 +8023,7 @@
         </is>
       </c>
       <c r="F167" s="5" t="n">
-        <v>-0.200574</v>
+        <v>-2.148661</v>
       </c>
       <c r="G167" t="inlineStr">
         <is>
@@ -8139,12 +8039,12 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>income (loss)</t>
+          <t>Cost of sales</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Shares issued on exercise of options 280,000 21,138 - - - 2</t>
+          <t>Exploration and evaluation expenses (4,177,925)</t>
         </is>
       </c>
       <c r="D168" t="inlineStr"/>
@@ -8154,7 +8054,7 @@
         </is>
       </c>
       <c r="F168" s="5" t="n">
-        <v>0.001138</v>
+        <v>-3.541044</v>
       </c>
       <c r="G168" t="inlineStr">
         <is>
@@ -8170,12 +8070,12 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>income (loss)</t>
+          <t>Cost of sales</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Transfer of option value - 11,358 (11,358) - -</t>
+          <t>General and administrative expenses (2,912,663)</t>
         </is>
       </c>
       <c r="D169" t="inlineStr"/>
@@ -8184,10 +8084,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F169" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F169" s="5" t="n">
+        <v>-2.282411</v>
       </c>
       <c r="G169" t="inlineStr">
         <is>
@@ -8203,12 +8101,12 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>income (loss)</t>
+          <t>Other income (expense)</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Share-based compensation - - 736,302 - -</t>
+          <t>Accretion and interest expense (40,478)</t>
         </is>
       </c>
       <c r="D170" t="inlineStr"/>
@@ -8218,7 +8116,7 @@
         </is>
       </c>
       <c r="F170" s="5" t="n">
-        <v>0.736302</v>
+        <v>-0.176405</v>
       </c>
       <c r="G170" t="inlineStr">
         <is>
@@ -8234,12 +8132,12 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>income (loss)</t>
+          <t>Other income (expense)</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Net loss - - - - (9,274,378)</t>
+          <t>Gain on settlement of accounts payable 11 4,753,730</t>
         </is>
       </c>
       <c r="D171" t="inlineStr"/>
@@ -8248,10 +8146,1272 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F171" s="5" t="n">
+      <c r="F171" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G171" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>Other income (expense)</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>Gain on change in provision for reclamation and rehabilitation 12 2,275,286</t>
+        </is>
+      </c>
+      <c r="D172" t="inlineStr"/>
+      <c r="E172" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F172" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G172" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>Other income (expense)</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>Gain on disposal of equipment 67,219</t>
+        </is>
+      </c>
+      <c r="D173" t="inlineStr"/>
+      <c r="E173" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F173" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G173" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>Other income (expense)</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>Extinguishment of gold stream arrangement 6 -</t>
+        </is>
+      </c>
+      <c r="D174" t="inlineStr"/>
+      <c r="E174" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F174" s="5" t="n">
+        <v>-20.641335</v>
+      </c>
+      <c r="G174" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>Other income (expense)</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>Transaction costs -</t>
+        </is>
+      </c>
+      <c r="D175" t="inlineStr"/>
+      <c r="E175" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F175" s="5" t="n">
+        <v>-0.518397</v>
+      </c>
+      <c r="G175" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>Other income (expense)</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>Foreign exchange loss (3,615,796)</t>
+        </is>
+      </c>
+      <c r="D176" t="inlineStr"/>
+      <c r="E176" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F176" s="5" t="n">
+        <v>3.459907</v>
+      </c>
+      <c r="G176" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>Other income (expense)</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>Interest income 517,681</t>
+        </is>
+      </c>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>InterestIncome</t>
+        </is>
+      </c>
+      <c r="E177" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F177" s="5" t="n">
+        <v>0.694931</v>
+      </c>
+      <c r="G177" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>Other income (expense)</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>Loss before income taxes (9,206,654)</t>
+        </is>
+      </c>
+      <c r="D178" t="inlineStr"/>
+      <c r="E178" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F178" s="5" t="n">
+        <v>-25.153415</v>
+      </c>
+      <c r="G178" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>Other income (expense)</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>Income tax expense 16 (67,724)</t>
+        </is>
+      </c>
+      <c r="D179" t="inlineStr"/>
+      <c r="E179" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F179" s="5" t="n">
+        <v>-0.075296</v>
+      </c>
+      <c r="G179" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>Other income (expense)</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>Loss for the period $ (9,274,378) $</t>
+        </is>
+      </c>
+      <c r="D180" t="inlineStr"/>
+      <c r="E180" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F180" s="5" t="n">
+        <v>-25.228711</v>
+      </c>
+      <c r="G180" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>Other comprehensive income (loss)</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>Loss for the period (9,274,378)</t>
+        </is>
+      </c>
+      <c r="D181" t="inlineStr"/>
+      <c r="E181" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F181" s="5" t="n">
+        <v>-25.228711</v>
+      </c>
+      <c r="G181" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>Other comprehensive income (loss)</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>Foreign currency translation adjustment 2,210,466</t>
+        </is>
+      </c>
+      <c r="D182" t="inlineStr"/>
+      <c r="E182" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F182" s="5" t="n">
+        <v>-1.053939</v>
+      </c>
+      <c r="G182" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>Other comprehensive income (loss)</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>Other comprehensive income (loss) for the period 2,210,466</t>
+        </is>
+      </c>
+      <c r="D183" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
+      <c r="E183" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F183" s="5" t="n">
+        <v>-1.053939</v>
+      </c>
+      <c r="G183" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>Other comprehensive income (loss)</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>Comprehensive loss for the period $ (7,063,912) $</t>
+        </is>
+      </c>
+      <c r="D184" t="inlineStr"/>
+      <c r="E184" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F184" s="5" t="n">
+        <v>-26.28265</v>
+      </c>
+      <c r="G184" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>Other comprehensive income (loss)</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>Weighted average common shares outstanding 498,802,983</t>
+        </is>
+      </c>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>SharesOutstanding</t>
+        </is>
+      </c>
+      <c r="E185" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F185" s="5" t="n">
+        <v>239.008432</v>
+      </c>
+      <c r="G185" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>shares                        surplus   comprehensive</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>Note</t>
+        </is>
+      </c>
+      <c r="D186" t="inlineStr"/>
+      <c r="E186" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F186" s="5" t="n">
+        <v>3e-06</v>
+      </c>
+      <c r="G186" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>income (loss)</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>Balance at May 1, 2017 191,995,896 $ 36,025,652 $ 6,420,268 $ 1,980,443 $ (35,917,567) $</t>
+        </is>
+      </c>
+      <c r="D187" t="inlineStr"/>
+      <c r="E187" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F187" s="5" t="n">
+        <v>8.508796</v>
+      </c>
+      <c r="G187" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>income (loss)</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>Shares issued on exercise of warrants 21,718 6,163 (2,425) - -</t>
+        </is>
+      </c>
+      <c r="D188" t="inlineStr"/>
+      <c r="E188" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F188" s="5" t="n">
+        <v>0.003738</v>
+      </c>
+      <c r="G188" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>income (loss)</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>Shares issued on exercise of options 86,306 23,696 (9,858) - -</t>
+        </is>
+      </c>
+      <c r="D189" t="inlineStr"/>
+      <c r="E189" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F189" s="5" t="n">
+        <v>0.013838</v>
+      </c>
+      <c r="G189" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>income (loss)</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>Share issue costs - (212) - - -</t>
+        </is>
+      </c>
+      <c r="D190" t="inlineStr"/>
+      <c r="E190" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F190" s="5" t="n">
+        <v>-0.000212</v>
+      </c>
+      <c r="G190" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>income (loss)</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>Share-based compensation - - 152,402 - -</t>
+        </is>
+      </c>
+      <c r="D191" t="inlineStr"/>
+      <c r="E191" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F191" s="5" t="n">
+        <v>0.152402</v>
+      </c>
+      <c r="G191" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>income (loss)</t>
+        </is>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>Net loss - - - - (3,069,964)</t>
+        </is>
+      </c>
+      <c r="D192" t="inlineStr"/>
+      <c r="E192" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F192" s="5" t="n">
+        <v>-3.069964</v>
+      </c>
+      <c r="G192" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>income (loss)</t>
+        </is>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>Other comprehensive loss - - - (1,559,530) -</t>
+        </is>
+      </c>
+      <c r="D193" t="inlineStr"/>
+      <c r="E193" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F193" s="5" t="n">
+        <v>-1.55953</v>
+      </c>
+      <c r="G193" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>income (loss)</t>
+        </is>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>Balance at May 1, 2018 192,103,920 $ 36,055,299 $ 6,560,387 $ 420,913 $ (38,987,531) $</t>
+        </is>
+      </c>
+      <c r="D194" t="inlineStr"/>
+      <c r="E194" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F194" s="5" t="n">
+        <v>4.049068</v>
+      </c>
+      <c r="G194" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>income (loss)</t>
+        </is>
+      </c>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>Shares issued on business combination 91,233,386 10,632,283 - - -</t>
+        </is>
+      </c>
+      <c r="D195" t="inlineStr"/>
+      <c r="E195" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F195" s="5" t="n">
+        <v>10.632283</v>
+      </c>
+      <c r="G195" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>income (loss)</t>
+        </is>
+      </c>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>Shares issued on private placement 30,000,000 3,416,338 - - -</t>
+        </is>
+      </c>
+      <c r="D196" t="inlineStr"/>
+      <c r="E196" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F196" s="5" t="n">
+        <v>3.416338</v>
+      </c>
+      <c r="G196" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>income (loss)</t>
+        </is>
+      </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>Share issue costs - (44,402) - - -</t>
+        </is>
+      </c>
+      <c r="D197" t="inlineStr"/>
+      <c r="E197" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F197" s="5" t="n">
+        <v>-0.044402</v>
+      </c>
+      <c r="G197" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>income (loss)</t>
+        </is>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>Shares issued on exercise of warrants 67,000 11,190 - - -</t>
+        </is>
+      </c>
+      <c r="D198" t="inlineStr"/>
+      <c r="E198" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F198" s="5" t="n">
+        <v>0.01119</v>
+      </c>
+      <c r="G198" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>income (loss)</t>
+        </is>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>Transfer of warrant value - 7,212 (7,212) - -</t>
+        </is>
+      </c>
+      <c r="D199" t="inlineStr"/>
+      <c r="E199" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F199" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G199" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>income (loss)</t>
+        </is>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>Share-based compensation - - 394,701 - -</t>
+        </is>
+      </c>
+      <c r="D200" t="inlineStr"/>
+      <c r="E200" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F200" s="5" t="n">
+        <v>0.394701</v>
+      </c>
+      <c r="G200" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>income (loss)</t>
+        </is>
+      </c>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>Net loss - - - - (25,228,711)</t>
+        </is>
+      </c>
+      <c r="D201" t="inlineStr"/>
+      <c r="E201" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F201" s="5" t="n">
+        <v>-25.228711</v>
+      </c>
+      <c r="G201" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>income (loss)</t>
+        </is>
+      </c>
+      <c r="C202" t="inlineStr">
+        <is>
+          <t>Other comprehensive loss - - - (1,053,939) -</t>
+        </is>
+      </c>
+      <c r="D202" t="inlineStr"/>
+      <c r="E202" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F202" s="5" t="n">
+        <v>-1.053939</v>
+      </c>
+      <c r="G202" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>income (loss)</t>
+        </is>
+      </c>
+      <c r="C203" t="inlineStr">
+        <is>
+          <t>Balance at April 30, 2019 313,404,306 $ 50,077,920 $ 6,947,876 $ (633,026) $ (64,216,242) $</t>
+        </is>
+      </c>
+      <c r="D203" t="inlineStr"/>
+      <c r="E203" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F203" s="5" t="n">
+        <v>-7.823472</v>
+      </c>
+      <c r="G203" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>income (loss)</t>
+        </is>
+      </c>
+      <c r="C204" t="inlineStr">
+        <is>
+          <t>Shares issued on rights offering 270,017,178 20,384,809 - - -</t>
+        </is>
+      </c>
+      <c r="D204" t="inlineStr"/>
+      <c r="E204" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F204" s="5" t="n">
+        <v>20.384809</v>
+      </c>
+      <c r="G204" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>income (loss)</t>
+        </is>
+      </c>
+      <c r="C205" t="inlineStr">
+        <is>
+          <t>Share issue costs - (200,574) - - -</t>
+        </is>
+      </c>
+      <c r="D205" t="inlineStr"/>
+      <c r="E205" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F205" s="5" t="n">
+        <v>-0.200574</v>
+      </c>
+      <c r="G205" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>income (loss)</t>
+        </is>
+      </c>
+      <c r="C206" t="inlineStr">
+        <is>
+          <t>Shares issued on exercise of options 280,000 21,138 - - -</t>
+        </is>
+      </c>
+      <c r="D206" t="inlineStr"/>
+      <c r="E206" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F206" s="5" t="n">
+        <v>0.021138</v>
+      </c>
+      <c r="G206" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>income (loss)</t>
+        </is>
+      </c>
+      <c r="C207" t="inlineStr">
+        <is>
+          <t>Transfer of option value - 11,358 (11,358) - -</t>
+        </is>
+      </c>
+      <c r="D207" t="inlineStr"/>
+      <c r="E207" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F207" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G207" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>income (loss)</t>
+        </is>
+      </c>
+      <c r="C208" t="inlineStr">
+        <is>
+          <t>Share-based compensation - - 736,302 - -</t>
+        </is>
+      </c>
+      <c r="D208" t="inlineStr"/>
+      <c r="E208" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F208" s="5" t="n">
+        <v>0.736302</v>
+      </c>
+      <c r="G208" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>income (loss)</t>
+        </is>
+      </c>
+      <c r="C209" t="inlineStr">
+        <is>
+          <t>Net loss - - - - (9,274,378)</t>
+        </is>
+      </c>
+      <c r="D209" t="inlineStr"/>
+      <c r="E209" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F209" s="5" t="n">
         <v>-9.274378</v>
       </c>
-      <c r="G171" t="inlineStr">
+      <c r="G209" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>income (loss)</t>
+        </is>
+      </c>
+      <c r="C210" t="inlineStr">
+        <is>
+          <t>Other comprehensive income - - - 2,210,466 -</t>
+        </is>
+      </c>
+      <c r="D210" t="inlineStr"/>
+      <c r="E210" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F210" s="5" t="n">
+        <v>2.210466</v>
+      </c>
+      <c r="G210" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>income (loss)</t>
+        </is>
+      </c>
+      <c r="C211" t="inlineStr">
+        <is>
+          <t>Balance at December 31, 2019 583,701,484 $ 70,294,651 $ 7,672,820 $ 1,577,440 $ (73,490,620) $</t>
+        </is>
+      </c>
+      <c r="D211" t="inlineStr"/>
+      <c r="E211" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F211" s="5" t="n">
+        <v>6.054291</v>
+      </c>
+      <c r="G211" t="inlineStr">
         <is>
           <t>-</t>
         </is>

--- a/output/pdf_financials_xlsx/MKO.xlsx
+++ b/output/pdf_financials_xlsx/MKO.xlsx
@@ -630,10 +630,10 @@
         </is>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>0.695</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>0.518</v>
       </c>
     </row>
     <row r="13">
@@ -920,10 +920,10 @@
         </is>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-25.304</v>
+        <v>-25.999</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-25.297</v>
+        <v>-25.815</v>
       </c>
     </row>
     <row r="28">
@@ -956,10 +956,10 @@
         </is>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-25.262</v>
+        <v>-25.957</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-25.236</v>
+        <v>-25.754</v>
       </c>
     </row>
     <row r="30">
@@ -974,10 +974,10 @@
         </is>
       </c>
       <c r="C30" s="3" t="n">
-        <v>-318.5222544445845</v>
+        <v>-327.2853360232001</v>
       </c>
       <c r="D30" s="3" t="n">
-        <v>-294.023068857043</v>
+        <v>-300.0582546895025</v>
       </c>
     </row>
     <row r="31">
@@ -6749,7 +6749,7 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
@@ -8334,7 +8334,7 @@
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E177" t="inlineStr">

--- a/output/pdf_financials_xlsx/MKO.xlsx
+++ b/output/pdf_financials_xlsx/MKO.xlsx
@@ -2282,10 +2282,10 @@
         </is>
       </c>
       <c r="C110" s="3" t="n">
-        <v>0</v>
+        <v>0.055</v>
       </c>
       <c r="D110" s="3" t="n">
-        <v>0</v>
+        <v>0.023</v>
       </c>
     </row>
     <row r="111">
@@ -4347,7 +4347,11 @@
           <t>Accretion expense 21</t>
         </is>
       </c>
-      <c r="D50" t="inlineStr"/>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
       <c r="E50" t="inlineStr">
         <is>
           <t>-</t>
@@ -5355,7 +5359,11 @@
           <t>Accretion expense 12 23,312</t>
         </is>
       </c>
-      <c r="D82" t="inlineStr"/>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
       <c r="E82" t="inlineStr">
         <is>
           <t>-</t>
